--- a/04_Figures/F06_prediction/modules/acute/lasso/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/acute/lasso/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -146,22 +146,16 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_blue</t>
+    <t xml:space="preserve">ME_brown</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_black</t>
+    <t xml:space="preserve">ME_pink</t>
   </si>
   <si>
     <t xml:space="preserve">ME_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_blue</t>
   </si>
   <si>
     <t xml:space="preserve">ME_greenyellow</t>
@@ -170,16 +164,19 @@
     <t xml:space="preserve">ME_magenta</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_pink</t>
+    <t xml:space="preserve">ME_purple</t>
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_brown</t>
+    <t xml:space="preserve">ME_turquoise</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_tan</t>
+    <t xml:space="preserve">ME_yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_black</t>
   </si>
 </sst>
 </file>
@@ -566,16 +563,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.225685841765617</v>
+        <v>-0.178619705249659</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.978571428571428</v>
+        <v>-0.882142857142857</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -599,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.225685841765617</v>
+        <v>-0.178619705249659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.978571428571428</v>
+        <v>-0.882142857142857</v>
       </c>
       <c r="J3" t="n">
-        <v>0.562189054726368</v>
+        <v>0.512437810945274</v>
       </c>
       <c r="K3" t="n">
-        <v>0.492537313432836</v>
+        <v>0.27363184079602</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.38483935220655</v>
+        <v>-0.668247184942487</v>
       </c>
       <c r="M3" t="n">
-        <v>0.719631242127601</v>
+        <v>1.57524679581644</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +637,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -673,7 +670,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -685,16 +682,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.243781094527363</v>
+        <v>0.223880597014925</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.359196628061544</v>
+        <v>-0.553284467350219</v>
       </c>
       <c r="M5" t="n">
-        <v>0.641698922590865</v>
+        <v>1.50165380003717</v>
       </c>
     </row>
     <row r="6">
@@ -714,7 +711,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -747,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
@@ -759,16 +756,16 @@
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.497512437810945</v>
+        <v>0.467661691542289</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.357591374246877</v>
+        <v>-0.618729266942424</v>
       </c>
       <c r="M7" t="n">
-        <v>0.672382910387637</v>
+        <v>1.79706942465212</v>
       </c>
     </row>
     <row r="8">
@@ -788,16 +785,16 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.548216394081482</v>
+        <v>-0.595540185681172</v>
       </c>
       <c r="I8" t="n">
-        <v>0.75</v>
+        <v>-0.717857142857143</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -821,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>0.548216394081482</v>
+        <v>-0.595540185681172</v>
       </c>
       <c r="I9" t="n">
-        <v>0.75</v>
+        <v>-0.717857142857143</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0149253731343284</v>
+        <v>0.825870646766169</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0099502487562189</v>
+        <v>0.189054726368159</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.346467201880195</v>
+        <v>-0.629926867006671</v>
       </c>
       <c r="M9" t="n">
-        <v>0.849000898193825</v>
+        <v>1.51185084926667</v>
       </c>
     </row>
     <row r="10">
@@ -862,13 +859,13 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.418177101725059</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I10" t="n">
         <v>-0.996415759077198</v>
@@ -895,28 +892,28 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.418177101725059</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I11" t="n">
         <v>-0.996415759077198</v>
       </c>
       <c r="J11" t="n">
-        <v>0.761194029850746</v>
+        <v>0.203980099502488</v>
       </c>
       <c r="K11" t="n">
-        <v>0.721393034825871</v>
+        <v>0.63681592039801</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.415802803259727</v>
+        <v>-0.609051224322725</v>
       </c>
       <c r="M11" t="n">
-        <v>0.828869475369538</v>
+        <v>1.69099636605214</v>
       </c>
     </row>
     <row r="12">
@@ -936,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -969,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
@@ -987,10 +984,10 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.294979148383638</v>
+        <v>-0.392679103873986</v>
       </c>
       <c r="M13" t="n">
-        <v>0.450909382030494</v>
+        <v>0.691799789875295</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.60159888046914</v>
       </c>
     </row>
     <row r="4">
@@ -1045,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.138696961511292</v>
       </c>
     </row>
     <row r="5">
@@ -1056,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.644151153129559</v>
+        <v>-1.16717448596064</v>
       </c>
     </row>
     <row r="6">
@@ -1078,7 +1075,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.174833620761562</v>
       </c>
     </row>
     <row r="8">
@@ -1100,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.263934265186734</v>
+        <v>-0.250785300934614</v>
       </c>
     </row>
     <row r="10">
@@ -1144,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0540407105300298</v>
+        <v>-0.183879136129574</v>
       </c>
     </row>
     <row r="14">
@@ -1155,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.772272404638393</v>
+        <v>-0.506040593080779</v>
       </c>
     </row>
     <row r="15">
@@ -1177,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.329228800648476</v>
+        <v>-0.320445488469068</v>
       </c>
     </row>
     <row r="17">
@@ -1199,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.241231124077486</v>
+        <v>-0.0415449222077737</v>
       </c>
     </row>
     <row r="19">
@@ -1210,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.482218196783673</v>
+        <v>-0.301183061570337</v>
       </c>
     </row>
     <row r="20">
@@ -1221,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.556416219901029</v>
+        <v>-0.255500578634317</v>
       </c>
     </row>
     <row r="21">
@@ -1232,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.280251146358411</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="22">
@@ -1243,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.521389083153554</v>
+        <v>-0.241977504099935</v>
       </c>
     </row>
     <row r="23">
@@ -1254,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.18178230634195</v>
+        <v>-1.19297145437163</v>
       </c>
     </row>
     <row r="24">
@@ -1265,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.554385809859872</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="25">
@@ -1298,7 +1295,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.57211893630173</v>
       </c>
     </row>
     <row r="28">
@@ -1309,7 +1306,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.152311659996687</v>
+        <v>-0.15744058447101</v>
       </c>
     </row>
     <row r="29">
@@ -1320,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.385651795167001</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="30">
@@ -1342,7 +1339,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.282180301186002</v>
+        <v>-0.11915033354754</v>
       </c>
     </row>
     <row r="32">
@@ -1364,7 +1361,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.229267507457656</v>
+        <v>-0.359932152948111</v>
       </c>
     </row>
     <row r="34">
@@ -1375,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.267855966036334</v>
+        <v>-0.174019970949994</v>
       </c>
     </row>
     <row r="35">
@@ -1386,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.576102399961699</v>
+        <v>-0.347295511660345</v>
       </c>
     </row>
     <row r="36">
@@ -1397,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.481785764977421</v>
+        <v>-0.837055980150393</v>
       </c>
     </row>
     <row r="37">
@@ -1408,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0946963558859413</v>
+        <v>0.00273011919218247</v>
       </c>
     </row>
     <row r="38">
@@ -1419,7 +1416,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0014061532263524</v>
+        <v>-0.863524678121811</v>
       </c>
     </row>
     <row r="39">
@@ -1441,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.131504593779628</v>
+        <v>-0.158465849748234</v>
       </c>
     </row>
     <row r="41">
@@ -1452,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.20183699553051</v>
+        <v>-0.511775844963263</v>
       </c>
     </row>
     <row r="42">
@@ -1463,7 +1460,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.930966354240026</v>
+        <v>-3.01160109047197</v>
       </c>
     </row>
     <row r="43">
@@ -1485,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.195418615115045</v>
+        <v>-0.979542180626997</v>
       </c>
     </row>
     <row r="45">
@@ -1496,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-3.62280948844578</v>
+        <v>-4.31882095791542</v>
       </c>
     </row>
     <row r="46">
@@ -1507,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.168954866310352</v>
+        <v>-0.190535404131854</v>
       </c>
     </row>
     <row r="47">
@@ -1518,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.413816768029113</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="48">
@@ -1529,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.231731975071952</v>
+        <v>-0.228530093173377</v>
       </c>
     </row>
     <row r="49">
@@ -1540,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.197264168459542</v>
+        <v>-0.296339888544693</v>
       </c>
     </row>
     <row r="50">
@@ -1551,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.13744922150974</v>
       </c>
     </row>
     <row r="51">
@@ -1562,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.225020874189225</v>
       </c>
     </row>
     <row r="52">
@@ -1584,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>0.550077714109794</v>
+        <v>-0.368711656551239</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.028325019284535</v>
+        <v>-0.30505587802314</v>
       </c>
     </row>
     <row r="55">
@@ -1606,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.181480755553578</v>
+        <v>-0.1792071291188</v>
       </c>
     </row>
     <row r="56">
@@ -1617,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.289818699792733</v>
+        <v>-0.373415420080572</v>
       </c>
     </row>
     <row r="57">
@@ -1628,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.911665734993278</v>
       </c>
     </row>
     <row r="58">
@@ -1639,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.264467748717158</v>
+        <v>-0.198701342443942</v>
       </c>
     </row>
     <row r="59">
@@ -1661,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.454532534951875</v>
+        <v>-4.29811888762436</v>
       </c>
     </row>
     <row r="61">
@@ -1672,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.256004052038289</v>
+        <v>-0.365619220952827</v>
       </c>
     </row>
     <row r="62">
@@ -1716,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-2.67441869167512</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="66">
@@ -1727,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.840824828393441</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="67">
@@ -1738,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.435798444656565</v>
       </c>
     </row>
     <row r="68">
@@ -1749,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.241969495437698</v>
+        <v>-0.170935975242186</v>
       </c>
     </row>
     <row r="69">
@@ -1760,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.337956991524206</v>
+        <v>-0.0653622246138295</v>
       </c>
     </row>
     <row r="70">
@@ -1771,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.537034489064107</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="71">
@@ -1782,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.281164225008524</v>
+        <v>-0.38926817634996</v>
       </c>
     </row>
     <row r="72">
@@ -1793,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.190917165195223</v>
+        <v>-0.176321558419997</v>
       </c>
     </row>
     <row r="73">
@@ -1804,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.198520210909892</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="74">
@@ -1815,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.994409406850368</v>
+        <v>-0.93831516962148</v>
       </c>
     </row>
     <row r="75">
@@ -1826,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.658788897396535</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="76">
@@ -1837,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.393849380723536</v>
+        <v>-0.245791508188669</v>
       </c>
     </row>
     <row r="77">
@@ -1848,7 +1845,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.14795918367347</v>
+        <v>-14.418458379427</v>
       </c>
     </row>
     <row r="78">
@@ -1859,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.16845665946824</v>
       </c>
     </row>
     <row r="79">
@@ -1870,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.34026427926741</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="80">
@@ -1881,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.814115654443397</v>
+        <v>-0.539650459249937</v>
       </c>
     </row>
     <row r="81">
@@ -1892,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>0.261009329632628</v>
+        <v>-0.200718384332014</v>
       </c>
     </row>
     <row r="82">
@@ -1903,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.224468109244926</v>
+        <v>-0.542229243926689</v>
       </c>
     </row>
     <row r="83">
@@ -1914,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.18702974867898</v>
+        <v>-4.46783851143086</v>
       </c>
     </row>
     <row r="84">
@@ -1925,7 +1922,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-1.09468843929229</v>
+        <v>-0.55353129553972</v>
       </c>
     </row>
     <row r="85">
@@ -1936,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.721308453573605</v>
       </c>
     </row>
     <row r="86">
@@ -1958,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.149326941542682</v>
+        <v>-0.144828804775705</v>
       </c>
     </row>
     <row r="88">
@@ -1980,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.512479991090688</v>
       </c>
     </row>
     <row r="90">
@@ -1991,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-1.10075588114069</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="91">
@@ -2002,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.36314201196311</v>
       </c>
     </row>
     <row r="92">
@@ -2013,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.562396376712966</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="93">
@@ -2035,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.34554528781757</v>
+        <v>-0.43730754848872</v>
       </c>
     </row>
     <row r="95">
@@ -2046,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>0.285839721441993</v>
+        <v>0.378564072115892</v>
       </c>
     </row>
     <row r="96">
@@ -2057,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.73577852389138</v>
+        <v>-0.434007905265517</v>
       </c>
     </row>
     <row r="97">
@@ -2068,7 +2065,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.163435206786231</v>
+        <v>-0.183668943488063</v>
       </c>
     </row>
     <row r="98">
@@ -2079,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.58860340922175</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="99">
@@ -2090,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.293750888881344</v>
+        <v>-4.97583435374876</v>
       </c>
     </row>
     <row r="100">
@@ -2101,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.560718416256495</v>
       </c>
     </row>
     <row r="101">
@@ -2112,7 +2109,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.374411096194839</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="102">
@@ -2123,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.171198066311178</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="103">
@@ -2134,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.0399215177586014</v>
+        <v>-0.163110629097508</v>
       </c>
     </row>
     <row r="104">
@@ -2145,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.329557401550993</v>
+        <v>-0.156147234208488</v>
       </c>
     </row>
     <row r="105">
@@ -2156,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.815351028427642</v>
+        <v>-0.377287177766203</v>
       </c>
     </row>
     <row r="106">
@@ -2167,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.247502263666113</v>
+        <v>-0.343632012804147</v>
       </c>
     </row>
     <row r="107">
@@ -2189,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.229198156072</v>
+        <v>-0.2095482159126</v>
       </c>
     </row>
     <row r="109">
@@ -2200,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>0.29439753192431</v>
+        <v>-0.419908590410335</v>
       </c>
     </row>
     <row r="110">
@@ -2211,7 +2208,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.163722299045003</v>
       </c>
     </row>
     <row r="111">
@@ -2233,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.296757338824488</v>
+        <v>-0.16121651502443</v>
       </c>
     </row>
     <row r="113">
@@ -2266,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.189501588752784</v>
+        <v>-0.178262419553616</v>
       </c>
     </row>
     <row r="116">
@@ -2277,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.219451134439718</v>
       </c>
     </row>
     <row r="117">
@@ -2288,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-1.1686050243545</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="118">
@@ -2299,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.27597692883177</v>
+        <v>-7.81542051984243</v>
       </c>
     </row>
     <row r="119">
@@ -2321,7 +2318,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.264979910630137</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="121">
@@ -2332,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.14795918367347</v>
+        <v>-4.97263917234673</v>
       </c>
     </row>
     <row r="122">
@@ -2343,7 +2340,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.235438552169096</v>
+        <v>-0.372674869098143</v>
       </c>
     </row>
     <row r="123">
@@ -2365,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.316369195141281</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="125">
@@ -2376,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.100425734460712</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="126">
@@ -2387,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.166503580326996</v>
+        <v>-0.192228736583337</v>
       </c>
     </row>
     <row r="127">
@@ -2398,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.325772721195079</v>
+        <v>-0.412029132287232</v>
       </c>
     </row>
     <row r="128">
@@ -2409,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.328585856291486</v>
+        <v>-0.392367549916895</v>
       </c>
     </row>
     <row r="129">
@@ -2431,7 +2428,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.150412309342204</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="131">
@@ -2442,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-2.07953585427273</v>
+        <v>-4.95692501377843</v>
       </c>
     </row>
     <row r="132">
@@ -2453,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.216273743894826</v>
+        <v>-0.272216341655142</v>
       </c>
     </row>
     <row r="133">
@@ -2486,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.904134246030719</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="136">
@@ -2497,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>-1.73557979027493</v>
+        <v>-0.828237021654527</v>
       </c>
     </row>
     <row r="137">
@@ -2508,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.353018043079164</v>
+        <v>-0.194668471748988</v>
       </c>
     </row>
     <row r="138">
@@ -2519,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.0938744638717941</v>
+        <v>-0.247846129767194</v>
       </c>
     </row>
     <row r="139">
@@ -2530,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.209141621875243</v>
       </c>
     </row>
     <row r="140">
@@ -2541,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.253660638955107</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="141">
@@ -2552,7 +2549,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.299602509614494</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="142">
@@ -2574,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.0069112238481</v>
       </c>
     </row>
     <row r="144">
@@ -2585,7 +2582,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.254465670371519</v>
       </c>
     </row>
     <row r="145">
@@ -2596,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.177517277896647</v>
+        <v>-0.17301580964385</v>
       </c>
     </row>
     <row r="146">
@@ -2607,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.953672186974116</v>
+        <v>-0.644666757136769</v>
       </c>
     </row>
     <row r="147">
@@ -2618,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.167642770829205</v>
+        <v>-0.15415703358328</v>
       </c>
     </row>
     <row r="148">
@@ -2640,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.728178325295115</v>
+        <v>-1.22899953095095</v>
       </c>
     </row>
     <row r="150">
@@ -2651,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.249384762317288</v>
+        <v>-0.378141840772561</v>
       </c>
     </row>
     <row r="151">
@@ -2662,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.259876815962985</v>
+        <v>-0.316806044951063</v>
       </c>
     </row>
     <row r="152">
@@ -2673,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.822728499846558</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="153">
@@ -2684,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-2.21236858354414</v>
+        <v>-0.195515519784663</v>
       </c>
     </row>
     <row r="154">
@@ -2695,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.170573066105706</v>
       </c>
     </row>
     <row r="155">
@@ -2717,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.801087579112232</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="157">
@@ -2728,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>0.221121115353587</v>
+        <v>-0.319524653743485</v>
       </c>
     </row>
     <row r="158">
@@ -2739,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.48538758870941</v>
       </c>
     </row>
     <row r="159">
@@ -2761,7 +2758,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.369857989581314</v>
+        <v>-0.481269517176423</v>
       </c>
     </row>
     <row r="161">
@@ -2772,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.471615753444666</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="162">
@@ -2794,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.0802124453845876</v>
+        <v>-0.247447415413383</v>
       </c>
     </row>
     <row r="164">
@@ -2805,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.280106756096261</v>
+        <v>-0.218491488281102</v>
       </c>
     </row>
     <row r="165">
@@ -2816,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.365430594103092</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="166">
@@ -2838,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-7.10823249093223</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="168">
@@ -2849,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.217251561675233</v>
+        <v>-4.42280180109268</v>
       </c>
     </row>
     <row r="169">
@@ -2860,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.136711657743895</v>
+        <v>-0.0425792212321849</v>
       </c>
     </row>
     <row r="170">
@@ -2871,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.332343280089061</v>
+        <v>-0.15699452809979</v>
       </c>
     </row>
     <row r="171">
@@ -2882,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.331101453485293</v>
+        <v>-0.590852104522525</v>
       </c>
     </row>
     <row r="172">
@@ -2893,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.638130096406499</v>
+        <v>-2.65803282935311</v>
       </c>
     </row>
     <row r="173">
@@ -2904,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.84324750904933</v>
       </c>
     </row>
     <row r="174">
@@ -2915,7 +2912,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.617258569315821</v>
+        <v>-7.86343310770122</v>
       </c>
     </row>
     <row r="175">
@@ -2926,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.300258296705273</v>
+        <v>-0.525911381887178</v>
       </c>
     </row>
     <row r="176">
@@ -2981,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.927862157762247</v>
+        <v>-0.248111418971802</v>
       </c>
     </row>
     <row r="181">
@@ -2992,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0716879895539094</v>
+        <v>-0.291224809817687</v>
       </c>
     </row>
     <row r="182">
@@ -3003,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.393504086477979</v>
+        <v>-0.14692244944926</v>
       </c>
     </row>
     <row r="183">
@@ -3014,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.0502362098673255</v>
+        <v>0.251678629300913</v>
       </c>
     </row>
     <row r="184">
@@ -3025,7 +3022,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.158127805199594</v>
+        <v>-1.45470171986627</v>
       </c>
     </row>
     <row r="185">
@@ -3047,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.276452241434133</v>
+        <v>-1.74710034844738</v>
       </c>
     </row>
     <row r="187">
@@ -3058,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.0883501930722506</v>
+        <v>-0.219061124972347</v>
       </c>
     </row>
     <row r="188">
@@ -3069,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.188391187139414</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="189">
@@ -3080,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.173164776115354</v>
+        <v>-0.338191314628943</v>
       </c>
     </row>
     <row r="190">
@@ -3091,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.175377282374542</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="191">
@@ -3102,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.440984058262227</v>
+        <v>-0.933935877173762</v>
       </c>
     </row>
     <row r="192">
@@ -3113,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.53874690173324</v>
+        <v>0.670434190938565</v>
       </c>
     </row>
     <row r="193">
@@ -3124,7 +3121,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.157796502755827</v>
       </c>
     </row>
     <row r="194">
@@ -3135,7 +3132,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.314102604003194</v>
+        <v>-0.179633289350454</v>
       </c>
     </row>
     <row r="195">
@@ -3146,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.510640199299795</v>
+        <v>-0.214024869286021</v>
       </c>
     </row>
     <row r="196">
@@ -3157,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-4.72118193844364</v>
+        <v>-0.549929225582131</v>
       </c>
     </row>
     <row r="197">
@@ -3168,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.181888099828042</v>
+        <v>-0.213549456020928</v>
       </c>
     </row>
     <row r="198">
@@ -3190,7 +3187,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.0940394265018152</v>
+        <v>-4.31787354595255</v>
       </c>
     </row>
     <row r="200">
@@ -3201,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.243458944998184</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="201">
@@ -3212,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.107897268013599</v>
+        <v>-0.842182773173936</v>
       </c>
     </row>
     <row r="202">
@@ -3223,7 +3220,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-1.86959608871174</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="203">
@@ -3234,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.47884302912436</v>
+        <v>-1.31105811861759</v>
       </c>
     </row>
     <row r="204">
@@ -3245,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.196023730110312</v>
+        <v>-0.200916423514765</v>
       </c>
     </row>
     <row r="205">
@@ -3256,7 +3253,7 @@
         <v>16</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.14795918367347</v>
+        <v>0.72772048283891</v>
       </c>
     </row>
     <row r="206">
@@ -3267,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.708544356411868</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="207">
@@ -3278,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.6148319696235</v>
       </c>
     </row>
     <row r="208">
@@ -3289,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.171051290009634</v>
       </c>
     </row>
     <row r="209">
@@ -3300,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.638367162986109</v>
+        <v>-0.524072778133135</v>
       </c>
     </row>
     <row r="210">
@@ -3322,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.605986389350486</v>
+        <v>-0.539131209859006</v>
       </c>
     </row>
     <row r="212">
@@ -3344,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.169006707275008</v>
+        <v>-0.339382381257111</v>
       </c>
     </row>
     <row r="214">
@@ -3355,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>0.20882757337835</v>
+        <v>0.453541622147996</v>
       </c>
     </row>
     <row r="215">
@@ -3366,7 +3363,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.284834284627983</v>
       </c>
     </row>
     <row r="216">
@@ -3377,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-2.35075607405534</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="217">
@@ -3399,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.0647491531941757</v>
+        <v>-0.0316334533371332</v>
       </c>
     </row>
     <row r="219">
@@ -3410,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.331606910996726</v>
+        <v>-0.208587233433253</v>
       </c>
     </row>
     <row r="220">
@@ -3421,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.513237117750619</v>
+        <v>-0.23251002234371</v>
       </c>
     </row>
     <row r="221">
@@ -3443,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.206805399443202</v>
       </c>
     </row>
     <row r="223">
@@ -3498,7 +3495,7 @@
         <v>16</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.157945749231381</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="228">
@@ -3509,7 +3506,7 @@
         <v>16</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.228487665455783</v>
+        <v>-0.186877248722815</v>
       </c>
     </row>
     <row r="229">
@@ -3520,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.461089281525594</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="230">
@@ -3531,7 +3528,7 @@
         <v>16</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.454861503660747</v>
       </c>
     </row>
     <row r="231">
@@ -3542,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.447305661967857</v>
+        <v>-1.67759910923332</v>
       </c>
     </row>
     <row r="232">
@@ -3553,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.394712402097278</v>
       </c>
     </row>
     <row r="233">
@@ -3564,7 +3561,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.235156387164531</v>
+        <v>-0.527788341424982</v>
       </c>
     </row>
     <row r="234">
@@ -3575,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.446964835189908</v>
       </c>
     </row>
     <row r="235">
@@ -3586,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.249741011103606</v>
+        <v>-0.317524524226714</v>
       </c>
     </row>
     <row r="236">
@@ -3597,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.213303588359287</v>
+        <v>-0.352164027640865</v>
       </c>
     </row>
     <row r="237">
@@ -3608,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.726499060840397</v>
+        <v>-1.37934960549293</v>
       </c>
     </row>
     <row r="238">
@@ -3619,7 +3616,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.14795918367347</v>
+        <v>0.2796766492212</v>
       </c>
     </row>
     <row r="239">
@@ -3630,7 +3627,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.168122641623159</v>
       </c>
     </row>
     <row r="240">
@@ -3641,7 +3638,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.125246571573794</v>
+        <v>-0.319333844789278</v>
       </c>
     </row>
     <row r="241">
@@ -3652,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-1.0839225711934</v>
+        <v>-0.513402844958489</v>
       </c>
     </row>
     <row r="242">
@@ -3663,7 +3660,7 @@
         <v>16</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.149710607066943</v>
+        <v>-1.00106592834397</v>
       </c>
     </row>
     <row r="243">
@@ -3674,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.13224976005581</v>
       </c>
     </row>
     <row r="244">
@@ -3685,7 +3682,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.529845462626499</v>
+        <v>-0.995099711706642</v>
       </c>
     </row>
     <row r="245">
@@ -3696,7 +3693,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.497683098775414</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="246">
@@ -3718,7 +3715,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.259655673541904</v>
       </c>
     </row>
     <row r="248">
@@ -3740,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.362985506699713</v>
+        <v>-0.474916615979092</v>
       </c>
     </row>
     <row r="250">
@@ -3751,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.557608981092409</v>
       </c>
     </row>
     <row r="251">
@@ -3762,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.210375368660783</v>
       </c>
     </row>
     <row r="252">
@@ -3784,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>0.217361391458801</v>
+        <v>-0.85295213740052</v>
       </c>
     </row>
     <row r="254">
@@ -3795,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.154118438222621</v>
+        <v>-0.171792057514418</v>
       </c>
     </row>
     <row r="255">
@@ -3806,7 +3803,7 @@
         <v>16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.232378313887459</v>
+        <v>-0.135208002191572</v>
       </c>
     </row>
     <row r="256">
@@ -3817,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.748681418434564</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="257">
@@ -3839,7 +3836,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.197314332512556</v>
+        <v>-2.36873238984617</v>
       </c>
     </row>
     <row r="259">
@@ -3850,7 +3847,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.165844315100637</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="260">
@@ -3861,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.737205776894449</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="261">
@@ -3872,7 +3869,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.184185198914682</v>
+        <v>-0.435381249174763</v>
       </c>
     </row>
     <row r="262">
@@ -3916,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.369612544026405</v>
+        <v>-0.512548237401954</v>
       </c>
     </row>
     <row r="266">
@@ -3927,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>0.432561609514286</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="267">
@@ -3938,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.344029145278035</v>
       </c>
     </row>
     <row r="268">
@@ -3949,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.0797708475068062</v>
+        <v>-0.713023069533209</v>
       </c>
     </row>
     <row r="269">
@@ -3960,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.140438482263041</v>
+        <v>-0.388812613771308</v>
       </c>
     </row>
     <row r="270">
@@ -3982,7 +3979,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.4205003726577</v>
+        <v>-0.180249365355858</v>
       </c>
     </row>
     <row r="272">
@@ -3993,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.298990967138972</v>
       </c>
     </row>
     <row r="273">
@@ -4015,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.821826489163523</v>
+        <v>-0.806675970350873</v>
       </c>
     </row>
     <row r="275">
@@ -4026,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.752393694638363</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="276">
@@ -4037,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.196444407268269</v>
+        <v>-17.3810711859226</v>
       </c>
     </row>
     <row r="277">
@@ -4048,7 +4045,7 @@
         <v>16</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.418149567996417</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="278">
@@ -4081,7 +4078,7 @@
         <v>16</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.314704059720083</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="281">
@@ -4092,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-1.43802853882667</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="282">
@@ -4103,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.229416171757306</v>
+        <v>-1.95682411043756</v>
       </c>
     </row>
     <row r="283">
@@ -4136,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.229359824748329</v>
       </c>
     </row>
     <row r="286">
@@ -4147,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.350347317208552</v>
+        <v>-0.419164506730528</v>
       </c>
     </row>
     <row r="287">
@@ -4158,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.161567077464281</v>
+        <v>-0.171241771913802</v>
       </c>
     </row>
     <row r="288">
@@ -4180,7 +4177,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.6386523289973</v>
       </c>
     </row>
     <row r="290">
@@ -4191,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-4.11928210472414</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="291">
@@ -4213,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.43545415651677</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="293">
@@ -4246,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.17614931965131</v>
+        <v>-0.218053454447917</v>
       </c>
     </row>
     <row r="296">
@@ -4257,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.53783613275829</v>
+        <v>0.177006766157691</v>
       </c>
     </row>
     <row r="297">
@@ -4290,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.386461179884323</v>
+        <v>-0.66204405096129</v>
       </c>
     </row>
     <row r="300">
@@ -4301,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.595820210719067</v>
+        <v>-0.616417428098046</v>
       </c>
     </row>
     <row r="301">
@@ -4312,7 +4309,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.53369736377207</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="302">
@@ -4323,7 +4320,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.564839639471313</v>
       </c>
     </row>
     <row r="303">
@@ -4334,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.534270993467269</v>
+        <v>-0.647256929494948</v>
       </c>
     </row>
     <row r="304">
@@ -4345,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.288902703060885</v>
+        <v>-0.856037316018345</v>
       </c>
     </row>
     <row r="305">
@@ -4356,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.66732653374727</v>
+        <v>-0.192539736722661</v>
       </c>
     </row>
     <row r="306">
@@ -4367,7 +4364,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.639767812252988</v>
+        <v>-0.299017879071615</v>
       </c>
     </row>
     <row r="307">
@@ -4378,7 +4375,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-1.04269306917798</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="308">
@@ -4389,7 +4386,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.402240146653897</v>
       </c>
     </row>
     <row r="309">
@@ -4400,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.70056115583963</v>
       </c>
     </row>
     <row r="310">
@@ -4433,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.649458511911431</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="313">
@@ -4444,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.276644123837321</v>
       </c>
     </row>
     <row r="314">
@@ -4455,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.607441334183441</v>
       </c>
     </row>
     <row r="315">
@@ -4466,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-1.30882017062206</v>
+        <v>-0.168208064433381</v>
       </c>
     </row>
     <row r="316">
@@ -4477,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.244952057243283</v>
       </c>
     </row>
     <row r="317">
@@ -4499,7 +4496,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.290342313193357</v>
+        <v>-0.24451951954766</v>
       </c>
     </row>
     <row r="319">
@@ -4510,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-1.15064440344745</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="320">
@@ -4532,7 +4529,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.390102358066299</v>
       </c>
     </row>
     <row r="322">
@@ -4543,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.203558024436949</v>
+        <v>-0.249224573804778</v>
       </c>
     </row>
     <row r="323">
@@ -4554,7 +4551,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.346382411873171</v>
       </c>
     </row>
     <row r="324">
@@ -4565,7 +4562,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.204196968922713</v>
+        <v>-0.238077302497897</v>
       </c>
     </row>
     <row r="325">
@@ -4587,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.274844002227961</v>
+        <v>-0.365068138663443</v>
       </c>
     </row>
     <row r="327">
@@ -4598,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.649466750376928</v>
+        <v>-0.361296863948536</v>
       </c>
     </row>
     <row r="328">
@@ -4609,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>0.204537693926865</v>
+        <v>-1.06712673930772</v>
       </c>
     </row>
     <row r="329">
@@ -4653,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.237950515543368</v>
+        <v>-0.468109812991738</v>
       </c>
     </row>
     <row r="333">
@@ -4675,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.98575096023176</v>
       </c>
     </row>
     <row r="335">
@@ -4708,7 +4705,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.147959183673469</v>
+        <v>-7.61281849486175</v>
       </c>
     </row>
     <row r="338">
@@ -4719,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.169108641462638</v>
       </c>
     </row>
     <row r="339">
@@ -4730,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.302459301365951</v>
+        <v>-0.308839500072509</v>
       </c>
     </row>
     <row r="340">
@@ -4741,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.174623785375223</v>
+        <v>-0.476165913119926</v>
       </c>
     </row>
     <row r="341">
@@ -4752,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.333816791613528</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="342">
@@ -4774,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.247308467338111</v>
+        <v>-0.157818355444729</v>
       </c>
     </row>
     <row r="344">
@@ -4785,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.287426357169967</v>
+        <v>-0.246301100165347</v>
       </c>
     </row>
     <row r="345">
@@ -4796,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.169570092302531</v>
+        <v>-0.20540497479633</v>
       </c>
     </row>
     <row r="346">
@@ -4807,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.587915386560663</v>
+        <v>-0.218761679625293</v>
       </c>
     </row>
     <row r="347">
@@ -4829,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.84153074474719</v>
       </c>
     </row>
     <row r="349">
@@ -4840,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.325599287847819</v>
       </c>
     </row>
     <row r="350">
@@ -4851,7 +4848,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.244571091824398</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="351">
@@ -4862,7 +4859,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.299104052436933</v>
+        <v>-0.865798500054598</v>
       </c>
     </row>
     <row r="352">
@@ -4873,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>0.1888914269851</v>
+        <v>-0.202321896478277</v>
       </c>
     </row>
     <row r="353">
@@ -4884,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-1.68872893564348</v>
+        <v>-0.181352138052072</v>
       </c>
     </row>
     <row r="354">
@@ -4895,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.18942015695345</v>
+        <v>-0.176930639827562</v>
       </c>
     </row>
     <row r="355">
@@ -4906,7 +4903,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.9298081819701</v>
       </c>
     </row>
     <row r="356">
@@ -4917,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-2.04407949166163</v>
+        <v>-0.521858259956492</v>
       </c>
     </row>
     <row r="357">
@@ -4928,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.367121878730969</v>
+        <v>-3.77052134574046</v>
       </c>
     </row>
     <row r="358">
@@ -4939,7 +4936,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.532079479269461</v>
       </c>
     </row>
     <row r="359">
@@ -4961,7 +4958,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.138681311378686</v>
+        <v>0.0203607267242937</v>
       </c>
     </row>
     <row r="361">
@@ -4972,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.167601975396619</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="362">
@@ -4994,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.398159661573788</v>
+        <v>-0.230385803920623</v>
       </c>
     </row>
     <row r="364">
@@ -5005,7 +5002,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.389729993147946</v>
+        <v>-0.415733155457654</v>
       </c>
     </row>
     <row r="365">
@@ -5016,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.175749912490588</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="366">
@@ -5038,7 +5035,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.261557451250228</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="368">
@@ -5049,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.0218310311723287</v>
+        <v>-0.320201988170539</v>
       </c>
     </row>
     <row r="369">
@@ -5060,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-6.41124815430501</v>
+        <v>-0.282639654022642</v>
       </c>
     </row>
     <row r="370">
@@ -5071,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.287368525104811</v>
+        <v>-0.376678781998249</v>
       </c>
     </row>
     <row r="371">
@@ -5082,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.184055631175008</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="372">
@@ -5093,7 +5090,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.206933801712284</v>
+        <v>-0.946692858590272</v>
       </c>
     </row>
     <row r="373">
@@ -5115,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.78278331560667</v>
       </c>
     </row>
     <row r="375">
@@ -5126,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>0.287856148782803</v>
+        <v>0.114801112550147</v>
       </c>
     </row>
     <row r="376">
@@ -5170,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.370319082659376</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="380">
@@ -5181,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.295337243450102</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="381">
@@ -5192,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.334200105619439</v>
+        <v>-0.310888927868955</v>
       </c>
     </row>
     <row r="382">
@@ -5203,7 +5200,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-2.77858076724223</v>
+        <v>0.0820329228011609</v>
       </c>
     </row>
     <row r="383">
@@ -5214,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.295905174243916</v>
+        <v>-0.357747773544361</v>
       </c>
     </row>
     <row r="384">
@@ -5225,7 +5222,7 @@
         <v>16</v>
       </c>
       <c r="C384" t="n">
-        <v>-1.00826423745753</v>
+        <v>-0.142429800046129</v>
       </c>
     </row>
     <row r="385">
@@ -5236,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.172702384306234</v>
       </c>
     </row>
     <row r="386">
@@ -5247,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.557701353936264</v>
+        <v>-5.46654304906474</v>
       </c>
     </row>
     <row r="387">
@@ -5258,7 +5255,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.245548028401058</v>
+        <v>-0.30881248852017</v>
       </c>
     </row>
     <row r="388">
@@ -5280,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.222302010045041</v>
+        <v>-1.34729113679233</v>
       </c>
     </row>
     <row r="390">
@@ -5291,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.335021305185383</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="391">
@@ -5302,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.0420010646787996</v>
+        <v>0.0215648637711887</v>
       </c>
     </row>
     <row r="392">
@@ -5313,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.462552675694299</v>
+        <v>-0.459598434821508</v>
       </c>
     </row>
     <row r="393">
@@ -5335,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.0530688764900888</v>
+        <v>-0.595201001446023</v>
       </c>
     </row>
     <row r="395">
@@ -5346,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>0.167194013644478</v>
+        <v>-0.0111731819014442</v>
       </c>
     </row>
     <row r="396">
@@ -5357,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.416029012586484</v>
+        <v>-0.39236606588186</v>
       </c>
     </row>
     <row r="397">
@@ -5379,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-1.10031536213582</v>
+        <v>-0.230043292116369</v>
       </c>
     </row>
     <row r="399">
@@ -5390,7 +5387,7 @@
         <v>16</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.0782692052874467</v>
+        <v>-0.749278836206524</v>
       </c>
     </row>
     <row r="400">
@@ -5401,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.212077382853733</v>
+        <v>-1.36872002463675</v>
       </c>
     </row>
     <row r="401">
@@ -5412,7 +5409,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.622783553880734</v>
       </c>
     </row>
     <row r="402">
@@ -5434,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-5.60082831592808</v>
+        <v>-0.111867358278965</v>
       </c>
     </row>
     <row r="404">
@@ -5445,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.157118439873064</v>
+        <v>-0.124815703546925</v>
       </c>
     </row>
     <row r="405">
@@ -5456,7 +5453,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.62257539853125</v>
       </c>
     </row>
     <row r="406">
@@ -5467,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.177657474561574</v>
       </c>
     </row>
     <row r="407">
@@ -5478,7 +5475,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.533740983217343</v>
+        <v>-1.38830907521177</v>
       </c>
     </row>
     <row r="408">
@@ -5489,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.179417918592077</v>
+        <v>-0.439532556964042</v>
       </c>
     </row>
     <row r="409">
@@ -5500,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.515497793073186</v>
+        <v>-1.70950189343923</v>
       </c>
     </row>
     <row r="410">
@@ -5522,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.617683625711076</v>
+        <v>-0.492204127350555</v>
       </c>
     </row>
     <row r="412">
@@ -5544,7 +5541,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>0.186401196525332</v>
+        <v>-0.717578200086235</v>
       </c>
     </row>
     <row r="414">
@@ -5555,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.214375198215179</v>
+        <v>0.0460923043616405</v>
       </c>
     </row>
     <row r="415">
@@ -5566,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.844994969508376</v>
+        <v>-0.185063550830777</v>
       </c>
     </row>
     <row r="416">
@@ -5577,7 +5574,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.33907597718288</v>
+        <v>-0.305115378411434</v>
       </c>
     </row>
     <row r="417">
@@ -5588,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.178060341167583</v>
+        <v>-0.316986348862938</v>
       </c>
     </row>
     <row r="418">
@@ -5599,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.149387026274236</v>
+        <v>-0.168677222704356</v>
       </c>
     </row>
     <row r="419">
@@ -5610,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.289505130855063</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="420">
@@ -5621,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-1.09104469042674</v>
+        <v>-0.199299758432805</v>
       </c>
     </row>
     <row r="421">
@@ -5654,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-1.6279820703459</v>
+        <v>-0.214275194294002</v>
       </c>
     </row>
     <row r="424">
@@ -5709,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.484029538485543</v>
+        <v>-0.165241311999288</v>
       </c>
     </row>
     <row r="429">
@@ -5720,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.542361071147256</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="430">
@@ -5742,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.425539699740239</v>
+        <v>-1.27087320080832</v>
       </c>
     </row>
     <row r="432">
@@ -5753,7 +5750,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.523687808642828</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="433">
@@ -5764,7 +5761,7 @@
         <v>16</v>
       </c>
       <c r="C433" t="n">
-        <v>-0.397626724779169</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="434">
@@ -5786,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.250402714392874</v>
+        <v>-0.26726428838434</v>
       </c>
     </row>
     <row r="436">
@@ -5797,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.227620866749614</v>
+        <v>-0.303973732737552</v>
       </c>
     </row>
     <row r="437">
@@ -5808,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.335958744434484</v>
+        <v>-0.366461562669496</v>
       </c>
     </row>
     <row r="438">
@@ -5819,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.572183952531006</v>
+        <v>-0.0823234606807681</v>
       </c>
     </row>
     <row r="439">
@@ -5830,7 +5827,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.226208026452435</v>
       </c>
     </row>
     <row r="440">
@@ -5841,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.25029074082727</v>
+        <v>-0.247974999558249</v>
       </c>
     </row>
     <row r="441">
@@ -5852,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-1.54327909906516</v>
+        <v>-0.711639820179658</v>
       </c>
     </row>
     <row r="442">
@@ -5874,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.97268884802105</v>
       </c>
     </row>
     <row r="444">
@@ -5885,7 +5882,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.13051080321648</v>
+        <v>-0.153007803906637</v>
       </c>
     </row>
     <row r="445">
@@ -5896,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.327863626874172</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="446">
@@ -5907,7 +5904,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.482408896979853</v>
       </c>
     </row>
     <row r="447">
@@ -5918,7 +5915,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.266580095865993</v>
       </c>
     </row>
     <row r="448">
@@ -5929,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.150375770082496</v>
+        <v>-0.0984812657642555</v>
       </c>
     </row>
     <row r="449">
@@ -5940,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.340754303473528</v>
+        <v>-2.83138295197806</v>
       </c>
     </row>
     <row r="450">
@@ -5951,7 +5948,7 @@
         <v>16</v>
       </c>
       <c r="C450" t="n">
-        <v>-0.933010054021536</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="451">
@@ -5984,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>0.0385579945229859</v>
+        <v>-0.487686116474751</v>
       </c>
     </row>
     <row r="454">
@@ -6006,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.255993560583824</v>
+        <v>-0.201491383148921</v>
       </c>
     </row>
     <row r="456">
@@ -6017,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.0340504604865546</v>
       </c>
     </row>
     <row r="457">
@@ -6039,7 +6036,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-1.22342618128111</v>
+        <v>-0.177925145053815</v>
       </c>
     </row>
     <row r="459">
@@ -6050,7 +6047,7 @@
         <v>16</v>
       </c>
       <c r="C459" t="n">
-        <v>-1.80764061366652</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="460">
@@ -6116,7 +6113,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.20024906544525</v>
+        <v>-0.503790968762517</v>
       </c>
     </row>
     <row r="466">
@@ -6127,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.174483940160423</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="467">
@@ -6149,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>0.38570965667457</v>
+        <v>-0.0667300243490387</v>
       </c>
     </row>
     <row r="469">
@@ -6160,7 +6157,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.316440286206036</v>
+        <v>-0.335377617368616</v>
       </c>
     </row>
     <row r="470">
@@ -6182,7 +6179,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.62535486657465</v>
+        <v>-0.133011870725106</v>
       </c>
     </row>
     <row r="472">
@@ -6193,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.293402804269451</v>
+        <v>-1.02609337563799</v>
       </c>
     </row>
     <row r="473">
@@ -6215,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.894450722943499</v>
+        <v>-0.37290594760051</v>
       </c>
     </row>
     <row r="475">
@@ -6237,7 +6234,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.147959183673469</v>
+        <v>-13.5436819963425</v>
       </c>
     </row>
     <row r="477">
@@ -6248,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.501349654632117</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="478">
@@ -6259,7 +6256,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.180585453848574</v>
+        <v>-0.177721231301453</v>
       </c>
     </row>
     <row r="479">
@@ -6270,7 +6267,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.443027617775967</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="480">
@@ -6281,7 +6278,7 @@
         <v>16</v>
       </c>
       <c r="C480" t="n">
-        <v>-0.342886552887345</v>
+        <v>-0.115499610888462</v>
       </c>
     </row>
     <row r="481">
@@ -6292,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.386998205410169</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="482">
@@ -6314,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.276704907290203</v>
       </c>
     </row>
     <row r="484">
@@ -6336,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.17231064078289</v>
       </c>
     </row>
     <row r="486">
@@ -6358,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.25787886259359</v>
+        <v>-0.309333371889418</v>
       </c>
     </row>
     <row r="488">
@@ -6380,7 +6377,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.07364938770846</v>
       </c>
     </row>
     <row r="490">
@@ -6391,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-1.45044141480205</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="491">
@@ -6424,7 +6421,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.07365796451489</v>
       </c>
     </row>
     <row r="494">
@@ -6446,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.155235598391841</v>
+        <v>-0.266918021754833</v>
       </c>
     </row>
     <row r="496">
@@ -6457,7 +6454,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>0.240196141448804</v>
+        <v>-0.250262532094231</v>
       </c>
     </row>
     <row r="497">
@@ -6490,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-1.57535536250451</v>
+        <v>0.162615215181444</v>
       </c>
     </row>
     <row r="500">
@@ -6501,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.580135855465316</v>
+        <v>-0.83673868065853</v>
       </c>
     </row>
     <row r="501">
@@ -6523,7 +6520,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-1.47600310719753</v>
+        <v>-2.90644226856023</v>
       </c>
     </row>
     <row r="503">
@@ -6534,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.772163683484512</v>
       </c>
     </row>
     <row r="504">
@@ -6545,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.18569770746174</v>
+        <v>-2.27911416096439</v>
       </c>
     </row>
     <row r="505">
@@ -6556,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>-1.23117890655251</v>
+        <v>-0.384752961495714</v>
       </c>
     </row>
     <row r="506">
@@ -6567,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.189226490515577</v>
       </c>
     </row>
     <row r="507">
@@ -6589,7 +6586,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.246895211479871</v>
+        <v>-0.252978277194647</v>
       </c>
     </row>
     <row r="509">
@@ -6600,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.01751825415765</v>
       </c>
     </row>
     <row r="510">
@@ -6611,7 +6608,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.147959183673469</v>
+        <v>-18.5839081442733</v>
       </c>
     </row>
     <row r="511">
@@ -6622,7 +6619,7 @@
         <v>16</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.689633039736355</v>
       </c>
     </row>
     <row r="512">
@@ -6644,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.92765921691257</v>
       </c>
     </row>
     <row r="514">
@@ -6666,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.153799467959446</v>
       </c>
     </row>
     <row r="516">
@@ -6699,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.19645556086998</v>
+        <v>-0.176356649213289</v>
       </c>
     </row>
     <row r="519">
@@ -6721,7 +6718,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.263024453583229</v>
       </c>
     </row>
     <row r="521">
@@ -6732,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.677958085708503</v>
       </c>
     </row>
     <row r="522">
@@ -6743,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.210685784928176</v>
       </c>
     </row>
     <row r="523">
@@ -6765,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.254237405682558</v>
+        <v>-0.28143483718625</v>
       </c>
     </row>
     <row r="525">
@@ -6776,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.174696057828407</v>
       </c>
     </row>
     <row r="526">
@@ -6798,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.89048273899602</v>
       </c>
     </row>
     <row r="528">
@@ -6809,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.072504422972727</v>
+        <v>-0.209394668435845</v>
       </c>
     </row>
     <row r="529">
@@ -6853,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.438056051530305</v>
+        <v>-0.583936919339954</v>
       </c>
     </row>
     <row r="533">
@@ -6908,7 +6905,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.205077604215471</v>
+        <v>-0.188392779948639</v>
       </c>
     </row>
     <row r="538">
@@ -6941,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-1.40464124894843</v>
+        <v>-0.452772929543289</v>
       </c>
     </row>
     <row r="541">
@@ -6952,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.265712390985658</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="542">
@@ -6974,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.177745226525763</v>
       </c>
     </row>
     <row r="544">
@@ -6996,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.374138230795394</v>
+        <v>-0.452681679114099</v>
       </c>
     </row>
     <row r="546">
@@ -7007,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.037437282056598</v>
+        <v>0.344711813892512</v>
       </c>
     </row>
     <row r="547">
@@ -7029,7 +7026,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.429602496844617</v>
       </c>
     </row>
     <row r="549">
@@ -7040,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.262904935262346</v>
+        <v>-1.22826816988488</v>
       </c>
     </row>
     <row r="550">
@@ -7062,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-3.5459952210633</v>
+        <v>-5.10928942677221</v>
       </c>
     </row>
     <row r="552">
@@ -7073,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.184646875518676</v>
+        <v>-0.176854537356373</v>
       </c>
     </row>
     <row r="553">
@@ -7084,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.154847771115501</v>
+        <v>-0.135818293488156</v>
       </c>
     </row>
     <row r="554">
@@ -7095,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.128639729660076</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="555">
@@ -7117,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.563214264800447</v>
+        <v>-1.51102602991402</v>
       </c>
     </row>
     <row r="557">
@@ -7128,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.214220571049501</v>
+        <v>-0.153724127194345</v>
       </c>
     </row>
     <row r="558">
@@ -7161,7 +7158,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.103897224933717</v>
+        <v>-0.049486868744175</v>
       </c>
     </row>
     <row r="561">
@@ -7194,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.494573060437797</v>
+        <v>-0.220783400230937</v>
       </c>
     </row>
     <row r="564">
@@ -7205,7 +7202,7 @@
         <v>16</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.560902449550668</v>
+        <v>-0.490407529638083</v>
       </c>
     </row>
     <row r="565">
@@ -7238,7 +7235,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.290530964662084</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="568">
@@ -7249,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.215003024269384</v>
+        <v>-0.368869106349653</v>
       </c>
     </row>
     <row r="569">
@@ -7260,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-5.58591249377261</v>
+        <v>-0.192051055273056</v>
       </c>
     </row>
     <row r="570">
@@ -7271,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.333537977570146</v>
+        <v>-0.546019110565432</v>
       </c>
     </row>
     <row r="571">
@@ -7293,7 +7290,7 @@
         <v>16</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.573173780469465</v>
+        <v>-2.12865667641991</v>
       </c>
     </row>
     <row r="573">
@@ -7315,7 +7312,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.159554472948974</v>
+        <v>-0.501422779179438</v>
       </c>
     </row>
     <row r="575">
@@ -7326,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.0842548376307692</v>
+        <v>-0.168022032875395</v>
       </c>
     </row>
     <row r="576">
@@ -7381,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.512798357065732</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="581">
@@ -7392,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.225199520785664</v>
+        <v>-2.21251592224185</v>
       </c>
     </row>
     <row r="582">
@@ -7403,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.29992380853281</v>
+        <v>-1.61572539579362</v>
       </c>
     </row>
     <row r="583">
@@ -7414,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.252101599357395</v>
+        <v>-0.224984327203817</v>
       </c>
     </row>
     <row r="584">
@@ -7425,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.335317004390927</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="585">
@@ -7436,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.211639507301456</v>
       </c>
     </row>
     <row r="586">
@@ -7447,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-2.34874453318615</v>
+        <v>-4.17662293049226</v>
       </c>
     </row>
     <row r="587">
@@ -7458,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.543019730701757</v>
+        <v>-0.287822023346144</v>
       </c>
     </row>
     <row r="588">
@@ -7469,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.229874361055897</v>
+        <v>-0.233373924179249</v>
       </c>
     </row>
     <row r="589">
@@ -7480,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.342989328996205</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="590">
@@ -7491,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.257503979478586</v>
+        <v>-3.20631661326221</v>
       </c>
     </row>
     <row r="591">
@@ -7502,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>0.0581574074574429</v>
+        <v>0.319937618129523</v>
       </c>
     </row>
     <row r="592">
@@ -7513,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.355547488031299</v>
       </c>
     </row>
     <row r="593">
@@ -7535,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.153608355791213</v>
+        <v>-0.211144484079657</v>
       </c>
     </row>
     <row r="595">
@@ -7546,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.168873954071961</v>
+        <v>0.031984745632993</v>
       </c>
     </row>
     <row r="596">
@@ -7557,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.0829767018859213</v>
+        <v>-0.184103640353722</v>
       </c>
     </row>
     <row r="597">
@@ -7579,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.199036526810388</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="599">
@@ -7590,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.155370029553934</v>
+        <v>-0.271403066109727</v>
       </c>
     </row>
     <row r="600">
@@ -7601,7 +7598,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.703513513360016</v>
       </c>
     </row>
     <row r="601">
@@ -7612,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.240651683252246</v>
+        <v>-1.07758454065253</v>
       </c>
     </row>
     <row r="602">
@@ -7623,7 +7620,7 @@
         <v>16</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.532258879974228</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="603">
@@ -7634,7 +7631,7 @@
         <v>16</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.95083350542407</v>
       </c>
     </row>
     <row r="604">
@@ -7667,7 +7664,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.191761913865867</v>
+        <v>-0.252111471297807</v>
       </c>
     </row>
     <row r="607">
@@ -7678,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.169997200304431</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="608">
@@ -7700,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.626582155729747</v>
+        <v>-0.519748120825819</v>
       </c>
     </row>
     <row r="610">
@@ -7722,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.316722416294692</v>
       </c>
     </row>
     <row r="612">
@@ -7744,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.953637959723279</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="614">
@@ -7755,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.389722356448243</v>
+        <v>-0.326302180244751</v>
       </c>
     </row>
     <row r="615">
@@ -7766,7 +7763,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.53451653114442</v>
+        <v>-0.784187768056449</v>
       </c>
     </row>
     <row r="616">
@@ -7777,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>0.557227613645434</v>
+        <v>0.676688394762176</v>
       </c>
     </row>
     <row r="617">
@@ -7799,7 +7796,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.257197882859577</v>
+        <v>-0.268957852711885</v>
       </c>
     </row>
     <row r="619">
@@ -7810,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>0.277742028699124</v>
+        <v>-0.667317325027422</v>
       </c>
     </row>
     <row r="620">
@@ -7821,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>0.302684005334063</v>
+        <v>-0.207293422222702</v>
       </c>
     </row>
     <row r="621">
@@ -7843,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.87670061537135</v>
       </c>
     </row>
     <row r="623">
@@ -7854,7 +7851,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.268467934322883</v>
+        <v>-0.238218328190307</v>
       </c>
     </row>
     <row r="624">
@@ -7865,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.64200454222437</v>
+        <v>-0.370254508951363</v>
       </c>
     </row>
     <row r="625">
@@ -7920,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.199376511841566</v>
       </c>
     </row>
     <row r="630">
@@ -7942,7 +7939,7 @@
         <v>16</v>
       </c>
       <c r="C631" t="n">
-        <v>-1.76879705171001</v>
+        <v>-0.125761166321564</v>
       </c>
     </row>
     <row r="632">
@@ -7964,7 +7961,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.253016300601359</v>
+        <v>-0.213729457215635</v>
       </c>
     </row>
     <row r="634">
@@ -7975,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.52500939740024</v>
       </c>
     </row>
     <row r="635">
@@ -7986,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.646023899109531</v>
+        <v>-0.159414451873969</v>
       </c>
     </row>
     <row r="636">
@@ -7997,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.321233783505073</v>
+        <v>-0.167943323167406</v>
       </c>
     </row>
     <row r="637">
@@ -8008,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.582189951018899</v>
+        <v>-0.656001505669849</v>
       </c>
     </row>
     <row r="638">
@@ -8019,7 +8016,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.379068679482208</v>
+        <v>-0.850998946627268</v>
       </c>
     </row>
     <row r="639">
@@ -8041,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.155902109949154</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="641">
@@ -8063,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.653974563228461</v>
+        <v>0.0849139251169716</v>
       </c>
     </row>
     <row r="643">
@@ -8096,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-10.9601437520951</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="646">
@@ -8107,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.219616760283231</v>
+        <v>-1.73977468561143</v>
       </c>
     </row>
     <row r="647">
@@ -8118,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.570639099411856</v>
+        <v>-8.6629213331523</v>
       </c>
     </row>
     <row r="648">
@@ -8129,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.368516593397449</v>
+        <v>-0.172127063060536</v>
       </c>
     </row>
     <row r="649">
@@ -8140,7 +8137,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-1.25141551108169</v>
+        <v>-1.66594873568804</v>
       </c>
     </row>
     <row r="650">
@@ -8151,7 +8148,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.328111452062511</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="651">
@@ -8195,7 +8192,7 @@
         <v>16</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.482915090544386</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="655">
@@ -8206,7 +8203,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.259737173847673</v>
+        <v>-0.28483392389516</v>
       </c>
     </row>
     <row r="656">
@@ -8217,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.32264837814887</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="657">
@@ -8250,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.643812006620451</v>
       </c>
     </row>
     <row r="660">
@@ -8261,7 +8258,7 @@
         <v>16</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.153984135121863</v>
+        <v>-0.136996335761215</v>
       </c>
     </row>
     <row r="661">
@@ -8272,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-1.43646226496327</v>
+        <v>-0.528846546381403</v>
       </c>
     </row>
     <row r="662">
@@ -8294,7 +8291,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-2.42559122777307</v>
+        <v>-1.5556577281174</v>
       </c>
     </row>
     <row r="664">
@@ -8305,7 +8302,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.295028608944777</v>
       </c>
     </row>
     <row r="665">
@@ -8371,7 +8368,7 @@
         <v>16</v>
       </c>
       <c r="C670" t="n">
-        <v>0.386254899377242</v>
+        <v>-0.0166262167551947</v>
       </c>
     </row>
     <row r="671">
@@ -8382,7 +8379,7 @@
         <v>16</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.12930714783844</v>
       </c>
     </row>
     <row r="672">
@@ -8393,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.431755198161119</v>
+        <v>-0.382193532971183</v>
       </c>
     </row>
     <row r="673">
@@ -8404,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-1.42845514757792</v>
+        <v>-0.969320481124118</v>
       </c>
     </row>
     <row r="674">
@@ -8415,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.658571743324285</v>
+        <v>-0.107328353593024</v>
       </c>
     </row>
     <row r="675">
@@ -8426,7 +8423,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.174515419656942</v>
       </c>
     </row>
     <row r="676">
@@ -8437,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>0.412625331669847</v>
+        <v>0.296909659236718</v>
       </c>
     </row>
     <row r="677">
@@ -8448,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.171424562092303</v>
+        <v>-0.105908490571817</v>
       </c>
     </row>
     <row r="678">
@@ -8459,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.266765867688451</v>
+        <v>-0.374876949774467</v>
       </c>
     </row>
     <row r="679">
@@ -8470,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.595370944050613</v>
+        <v>-0.294285800799489</v>
       </c>
     </row>
     <row r="680">
@@ -8481,7 +8478,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.202555026133459</v>
+        <v>-0.187419137765308</v>
       </c>
     </row>
     <row r="681">
@@ -8492,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.188046443887717</v>
+        <v>-0.20583359323901</v>
       </c>
     </row>
     <row r="682">
@@ -8503,7 +8500,7 @@
         <v>16</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.157130348405458</v>
+        <v>-0.132223424133286</v>
       </c>
     </row>
     <row r="683">
@@ -8514,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.832460951427613</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="684">
@@ -8525,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>0.169774147049661</v>
+        <v>0.143006876375095</v>
       </c>
     </row>
     <row r="685">
@@ -8569,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.326054273304935</v>
+        <v>-1.93611426908496</v>
       </c>
     </row>
     <row r="689">
@@ -8591,7 +8588,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-1.08538392049989</v>
+        <v>-0.84707475768595</v>
       </c>
     </row>
     <row r="691">
@@ -8602,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.455405464865419</v>
       </c>
     </row>
     <row r="692">
@@ -8613,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.284798078129111</v>
+        <v>-0.461703352350507</v>
       </c>
     </row>
     <row r="693">
@@ -8624,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.283456915728554</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="694">
@@ -8635,7 +8632,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.786342470775945</v>
+        <v>-0.818819312601046</v>
       </c>
     </row>
     <row r="695">
@@ -8646,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.137629247817122</v>
       </c>
     </row>
     <row r="696">
@@ -8657,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.285312950640182</v>
+        <v>-3.31378543672517</v>
       </c>
     </row>
     <row r="697">
@@ -8668,7 +8665,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.243116588279682</v>
       </c>
     </row>
     <row r="698">
@@ -8679,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.189012703011938</v>
+        <v>-0.344150544753744</v>
       </c>
     </row>
     <row r="699">
@@ -8701,7 +8698,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.29265046835582</v>
+        <v>-0.269159523731773</v>
       </c>
     </row>
     <row r="701">
@@ -8712,7 +8709,7 @@
         <v>16</v>
       </c>
       <c r="C701" t="n">
-        <v>-1.24506204015609</v>
+        <v>-0.312658717966002</v>
       </c>
     </row>
     <row r="702">
@@ -8723,7 +8720,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.170292061406562</v>
       </c>
     </row>
     <row r="703">
@@ -8745,7 +8742,7 @@
         <v>16</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.224300152330628</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="705">
@@ -8789,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.193079021649653</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="709">
@@ -8800,7 +8797,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.694247101858884</v>
+        <v>-0.67679651025502</v>
       </c>
     </row>
     <row r="710">
@@ -8811,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>0.691868921273389</v>
+        <v>0.709011648951297</v>
       </c>
     </row>
     <row r="711">
@@ -8822,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-2.27116516204209</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="712">
@@ -8833,7 +8830,7 @@
         <v>16</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.293710077401852</v>
       </c>
     </row>
     <row r="713">
@@ -8844,7 +8841,7 @@
         <v>16</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.167940970977924</v>
       </c>
     </row>
     <row r="714">
@@ -8855,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>0.0696130617561492</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="715">
@@ -8866,7 +8863,7 @@
         <v>16</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.15950329042669</v>
+        <v>-9.93605432401142</v>
       </c>
     </row>
     <row r="716">
@@ -8877,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>0.344929966827522</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="717">
@@ -8888,7 +8885,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.157753242414295</v>
+        <v>-0.157819144097538</v>
       </c>
     </row>
     <row r="718">
@@ -8899,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.69274068496101</v>
       </c>
     </row>
     <row r="719">
@@ -8910,7 +8907,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.198549618394168</v>
+        <v>-0.173358406027211</v>
       </c>
     </row>
     <row r="720">
@@ -8921,7 +8918,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.178756424615824</v>
+        <v>-0.221874595743727</v>
       </c>
     </row>
     <row r="721">
@@ -8943,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>0.17549648258732</v>
+        <v>-0.904549560480823</v>
       </c>
     </row>
     <row r="723">
@@ -8954,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.447646130692893</v>
+        <v>-0.233960617507087</v>
       </c>
     </row>
     <row r="724">
@@ -8976,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.355120680944027</v>
+        <v>-0.235555866704651</v>
       </c>
     </row>
     <row r="726">
@@ -8998,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.719413116892264</v>
+        <v>-0.182980455096515</v>
       </c>
     </row>
     <row r="728">
@@ -9009,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.000713776700824065</v>
+        <v>-0.116432777886171</v>
       </c>
     </row>
     <row r="729">
@@ -9020,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.323329533143076</v>
+        <v>-0.229959163050989</v>
       </c>
     </row>
     <row r="730">
@@ -9031,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.361302543301958</v>
+        <v>-0.439019098677313</v>
       </c>
     </row>
     <row r="731">
@@ -9053,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.229164848847383</v>
+        <v>-0.298393468949649</v>
       </c>
     </row>
     <row r="733">
@@ -9064,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.23608341304846</v>
       </c>
     </row>
     <row r="734">
@@ -9075,7 +9072,7 @@
         <v>16</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.0603797870954883</v>
       </c>
     </row>
     <row r="735">
@@ -9097,7 +9094,7 @@
         <v>16</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.197337862180119</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="737">
@@ -9119,7 +9116,7 @@
         <v>16</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.680336990874518</v>
+        <v>-0.979891709685204</v>
       </c>
     </row>
     <row r="739">
@@ -9130,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.148964070579813</v>
+        <v>-0.159691543184115</v>
       </c>
     </row>
     <row r="740">
@@ -9141,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.359785686192378</v>
+        <v>-1.44182319799964</v>
       </c>
     </row>
     <row r="741">
@@ -9152,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.393604841781759</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="742">
@@ -9174,7 +9171,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.270735459040877</v>
       </c>
     </row>
     <row r="744">
@@ -9185,7 +9182,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.514487563244243</v>
+        <v>-8.14289176432132</v>
       </c>
     </row>
     <row r="745">
@@ -9196,7 +9193,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.93279160209293</v>
+        <v>-2.4260004944661</v>
       </c>
     </row>
     <row r="746">
@@ -9218,7 +9215,7 @@
         <v>16</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.325388789838919</v>
+        <v>-0.302709632226934</v>
       </c>
     </row>
     <row r="748">
@@ -9240,7 +9237,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.284613949640238</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="750">
@@ -9251,7 +9248,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.0772529850260202</v>
+        <v>-4.05000895102116</v>
       </c>
     </row>
     <row r="751">
@@ -9273,7 +9270,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.383153727322293</v>
+        <v>-0.319255666139604</v>
       </c>
     </row>
     <row r="753">
@@ -9284,7 +9281,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>0.0733004494532299</v>
+        <v>-0.581735746251934</v>
       </c>
     </row>
     <row r="754">
@@ -9295,7 +9292,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.431158895569442</v>
       </c>
     </row>
     <row r="755">
@@ -9306,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.193978710775517</v>
+        <v>-0.217435591093795</v>
       </c>
     </row>
     <row r="756">
@@ -9317,7 +9314,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.194912548096055</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="757">
@@ -9328,7 +9325,7 @@
         <v>16</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.452945147191188</v>
+        <v>-0.423421182923219</v>
       </c>
     </row>
     <row r="758">
@@ -9339,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.449563026880744</v>
+        <v>-0.173215555473304</v>
       </c>
     </row>
     <row r="759">
@@ -9350,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.371825174555223</v>
+        <v>-8.78262930530455</v>
       </c>
     </row>
     <row r="760">
@@ -9361,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.471301801631372</v>
       </c>
     </row>
     <row r="761">
@@ -9372,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.128927255245476</v>
+        <v>-1.09832355887741</v>
       </c>
     </row>
     <row r="762">
@@ -9383,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.356144460673768</v>
+        <v>-0.0663475900900159</v>
       </c>
     </row>
     <row r="763">
@@ -9394,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>0.126234795990268</v>
+        <v>-0.137276697573785</v>
       </c>
     </row>
     <row r="764">
@@ -9405,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.291329712947777</v>
       </c>
     </row>
     <row r="765">
@@ -9416,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.320530016909898</v>
+        <v>-7.37245116374067</v>
       </c>
     </row>
     <row r="766">
@@ -9427,7 +9424,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.343607817613686</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="767">
@@ -9449,7 +9446,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.82292599074149</v>
+        <v>-1.80069007731292</v>
       </c>
     </row>
     <row r="769">
@@ -9460,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.848009565011204</v>
+        <v>-0.516653639613726</v>
       </c>
     </row>
     <row r="770">
@@ -9482,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.707704658227158</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="772">
@@ -9493,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.129566339202757</v>
+        <v>-0.241749214273774</v>
       </c>
     </row>
     <row r="773">
@@ -9504,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.43037562083692</v>
       </c>
     </row>
     <row r="774">
@@ -9526,7 +9523,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-1.25638010761987</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="776">
@@ -9537,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.147989083387627</v>
+        <v>-0.161527720689285</v>
       </c>
     </row>
     <row r="777">
@@ -9559,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.272592191193009</v>
+        <v>-0.284135059496624</v>
       </c>
     </row>
     <row r="779">
@@ -9570,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>-1.44562453941526</v>
+        <v>-0.378636491205824</v>
       </c>
     </row>
     <row r="780">
@@ -9581,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.000430701435823133</v>
+        <v>-0.222250492670556</v>
       </c>
     </row>
     <row r="781">
@@ -9592,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.216959634540948</v>
+        <v>-0.405658536829242</v>
       </c>
     </row>
     <row r="782">
@@ -9614,7 +9611,7 @@
         <v>16</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.315525850451124</v>
+        <v>-0.754698521304325</v>
       </c>
     </row>
     <row r="784">
@@ -9625,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.0561850569618627</v>
+        <v>-0.0957847429828163</v>
       </c>
     </row>
     <row r="785">
@@ -9647,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-1.22759025885977</v>
+        <v>-3.1865256278035</v>
       </c>
     </row>
     <row r="787">
@@ -9680,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.304970957601189</v>
+        <v>-0.178918366037657</v>
       </c>
     </row>
     <row r="790">
@@ -9713,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.79803556170491</v>
+        <v>-0.443144577338401</v>
       </c>
     </row>
     <row r="793">
@@ -9724,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.228496071599874</v>
+        <v>-0.19202532421664</v>
       </c>
     </row>
     <row r="794">
@@ -9735,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.0648327005337</v>
       </c>
     </row>
     <row r="795">
@@ -9746,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.176097403044715</v>
+        <v>-0.24068695108858</v>
       </c>
     </row>
     <row r="796">
@@ -9768,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>0.0988247169546177</v>
+        <v>0.160022821832676</v>
       </c>
     </row>
     <row r="798">
@@ -9801,7 +9798,7 @@
         <v>16</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.00746015515980103</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="801">
@@ -9823,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.432626228071999</v>
+        <v>-0.456599941130931</v>
       </c>
     </row>
     <row r="803">
@@ -9834,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.192151548234764</v>
+        <v>-0.259482845268099</v>
       </c>
     </row>
     <row r="804">
@@ -9845,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.154428590015564</v>
+        <v>-2.51045886277383</v>
       </c>
     </row>
     <row r="805">
@@ -9856,7 +9853,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.748311397275916</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="806">
@@ -9867,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.388693401200363</v>
       </c>
     </row>
     <row r="807">
@@ -9878,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.821999106521551</v>
+        <v>-0.0603328102789444</v>
       </c>
     </row>
     <row r="808">
@@ -9889,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.375634127701247</v>
+        <v>-0.387422871247581</v>
       </c>
     </row>
     <row r="809">
@@ -9900,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.329325895077013</v>
+        <v>-0.442156125299663</v>
       </c>
     </row>
     <row r="810">
@@ -9911,7 +9908,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.210123101344565</v>
+        <v>-0.189840033425948</v>
       </c>
     </row>
     <row r="811">
@@ -9922,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.434702461059484</v>
+        <v>-0.616365743416208</v>
       </c>
     </row>
     <row r="812">
@@ -9944,7 +9941,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-1.10602789928804</v>
+        <v>-0.265011460264432</v>
       </c>
     </row>
     <row r="814">
@@ -9955,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.348768711628407</v>
+        <v>-0.400257530013195</v>
       </c>
     </row>
     <row r="815">
@@ -9966,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.83956238501399</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="816">
@@ -9977,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>0.461550017514115</v>
+        <v>-0.260789457735836</v>
       </c>
     </row>
     <row r="817">
@@ -10010,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-1.1069743777384</v>
+        <v>-2.04285901766506</v>
       </c>
     </row>
     <row r="820">
@@ -10021,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.240005327462952</v>
       </c>
     </row>
     <row r="821">
@@ -10032,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.511965218584498</v>
+        <v>-0.098475716252256</v>
       </c>
     </row>
     <row r="822">
@@ -10043,7 +10040,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.185518401213822</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="823">
@@ -10065,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.253132978799162</v>
+        <v>-0.286107581848502</v>
       </c>
     </row>
     <row r="825">
@@ -10076,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.172932831178247</v>
+        <v>-0.177641678393002</v>
       </c>
     </row>
     <row r="826">
@@ -10087,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.226209935794779</v>
+        <v>-0.220724814712018</v>
       </c>
     </row>
     <row r="827">
@@ -10098,7 +10095,7 @@
         <v>16</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.196958426536715</v>
+        <v>-1.68696645192542</v>
       </c>
     </row>
     <row r="828">
@@ -10109,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.289440332631712</v>
+        <v>-0.243052213277746</v>
       </c>
     </row>
     <row r="829">
@@ -10120,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.58591999424164</v>
+        <v>-0.147114153653935</v>
       </c>
     </row>
     <row r="830">
@@ -10131,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.169583342749704</v>
+        <v>-0.174670535772393</v>
       </c>
     </row>
     <row r="831">
@@ -10142,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.191429477345765</v>
+        <v>-0.0560811839128004</v>
       </c>
     </row>
     <row r="832">
@@ -10164,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.370984328291149</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="834">
@@ -10186,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.245656456650293</v>
+        <v>-0.47045777945585</v>
       </c>
     </row>
     <row r="836">
@@ -10197,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.411498830738599</v>
+        <v>-0.273062502729983</v>
       </c>
     </row>
     <row r="837">
@@ -10208,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.251527225432692</v>
+        <v>-0.775186547058512</v>
       </c>
     </row>
     <row r="838">
@@ -10230,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.625364105868805</v>
+        <v>-0.570558095543721</v>
       </c>
     </row>
     <row r="840">
@@ -10252,7 +10249,7 @@
         <v>16</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.220754841828035</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="842">
@@ -10274,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.759524747933068</v>
+        <v>-0.266042826863846</v>
       </c>
     </row>
     <row r="844">
@@ -10285,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.15711490994539</v>
+        <v>-0.190616664622272</v>
       </c>
     </row>
     <row r="845">
@@ -10318,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.220118472088865</v>
+        <v>-0.25221609398503</v>
       </c>
     </row>
     <row r="848">
@@ -10329,7 +10326,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.229628917452088</v>
+        <v>-0.229720678710484</v>
       </c>
     </row>
     <row r="849">
@@ -10340,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.213099648201619</v>
+        <v>-0.182480825908796</v>
       </c>
     </row>
     <row r="850">
@@ -10351,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.97996522912195</v>
       </c>
     </row>
     <row r="851">
@@ -10362,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.433943710191553</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="852">
@@ -10373,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.186826318181437</v>
+        <v>-0.774658035190512</v>
       </c>
     </row>
     <row r="853">
@@ -10395,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.245958255214726</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="855">
@@ -10406,7 +10403,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.6557887452723</v>
+        <v>-0.261431110958309</v>
       </c>
     </row>
     <row r="856">
@@ -10417,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.27588217892729</v>
+        <v>-0.300097505581681</v>
       </c>
     </row>
     <row r="857">
@@ -10428,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.73162175018627</v>
       </c>
     </row>
     <row r="858">
@@ -10439,7 +10436,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.25065504862278</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="859">
@@ -10450,7 +10447,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.947958097451946</v>
+        <v>-0.195502529698853</v>
       </c>
     </row>
     <row r="860">
@@ -10461,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-1.49202596230169</v>
+        <v>-0.486912330500587</v>
       </c>
     </row>
     <row r="861">
@@ -10472,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.177138201196351</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="862">
@@ -10483,7 +10480,7 @@
         <v>16</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.174113997221985</v>
+        <v>-0.605629942324548</v>
       </c>
     </row>
     <row r="863">
@@ -10494,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.344865748047004</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="864">
@@ -10505,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>0.0632846911875612</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="865">
@@ -10516,7 +10513,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.361989540193915</v>
       </c>
     </row>
     <row r="866">
@@ -10527,7 +10524,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.14795918367347</v>
+        <v>-7.05372593161751</v>
       </c>
     </row>
     <row r="867">
@@ -10538,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.64836478815177</v>
       </c>
     </row>
     <row r="868">
@@ -10560,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.483404350196921</v>
+        <v>-0.277374787227268</v>
       </c>
     </row>
     <row r="870">
@@ -10582,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-1.19937534386242</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="872">
@@ -10593,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-9.45950052284201</v>
+        <v>-0.195058026652756</v>
       </c>
     </row>
     <row r="873">
@@ -10626,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.336032118863552</v>
+        <v>-0.194308102125863</v>
       </c>
     </row>
     <row r="876">
@@ -10637,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-2.39858031678581</v>
+        <v>0.358096970414064</v>
       </c>
     </row>
     <row r="877">
@@ -10648,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.251313936904029</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="878">
@@ -10670,7 +10667,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.202704305009829</v>
       </c>
     </row>
     <row r="880">
@@ -10681,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.505780708113537</v>
+        <v>-0.361568884213173</v>
       </c>
     </row>
     <row r="881">
@@ -10692,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.929460476015998</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="882">
@@ -10703,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.303699554692461</v>
       </c>
     </row>
     <row r="883">
@@ -10714,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.190410235669273</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="884">
@@ -10725,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.280663265068137</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="885">
@@ -10736,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.478902212206417</v>
+        <v>-0.181605139806449</v>
       </c>
     </row>
     <row r="886">
@@ -10747,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.300548868975617</v>
       </c>
     </row>
     <row r="887">
@@ -10769,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.196057516688351</v>
+        <v>-0.750696612982876</v>
       </c>
     </row>
     <row r="889">
@@ -10780,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.170618906382048</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="890">
@@ -10802,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>0.0759710620968799</v>
+        <v>0.322713283810268</v>
       </c>
     </row>
     <row r="892">
@@ -10813,7 +10810,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>0.0564976546252591</v>
+        <v>-0.19531290494464</v>
       </c>
     </row>
     <row r="893">
@@ -10824,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.186865292935682</v>
+        <v>-0.257463142683101</v>
       </c>
     </row>
     <row r="894">
@@ -10835,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.571542620005454</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="895">
@@ -10857,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.181092802368437</v>
+        <v>-0.95812295727816</v>
       </c>
     </row>
     <row r="897">
@@ -10868,7 +10865,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.214845875329365</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="898">
@@ -10890,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>0.0438807667540612</v>
+        <v>-0.55997737211158</v>
       </c>
     </row>
     <row r="900">
@@ -10901,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.783001411814026</v>
+        <v>-0.564350724975359</v>
       </c>
     </row>
     <row r="901">
@@ -10912,7 +10909,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.379566373547244</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="902">
@@ -10923,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.268738092820116</v>
+        <v>-0.159384639701162</v>
       </c>
     </row>
     <row r="903">
@@ -10934,7 +10931,7 @@
         <v>16</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.508208224279596</v>
+        <v>-0.176778638290364</v>
       </c>
     </row>
     <row r="904">
@@ -10945,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-1.24192710376041</v>
+        <v>-2.43118362229787</v>
       </c>
     </row>
     <row r="905">
@@ -10967,7 +10964,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-1.24460945236126</v>
+        <v>-0.224855040186575</v>
       </c>
     </row>
     <row r="907">
@@ -10978,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.324585590628331</v>
+        <v>-1.1195214106918</v>
       </c>
     </row>
     <row r="908">
@@ -10989,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.33516537960153</v>
+        <v>-0.555387588234614</v>
       </c>
     </row>
     <row r="909">
@@ -11011,7 +11008,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.316458832960882</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="911">
@@ -11022,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.282795978583218</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="912">
@@ -11055,7 +11052,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.562727964115252</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="915">
@@ -11066,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.34241937503183</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="916">
@@ -11077,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.426808617930234</v>
+        <v>-0.249093370145629</v>
       </c>
     </row>
     <row r="917">
@@ -11088,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.300949138277794</v>
+        <v>-0.365496214774238</v>
       </c>
     </row>
     <row r="918">
@@ -11110,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.391665259908387</v>
+        <v>-17.4264833506066</v>
       </c>
     </row>
     <row r="920">
@@ -11121,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.300358681956234</v>
+        <v>-1.10723526789555</v>
       </c>
     </row>
     <row r="921">
@@ -11154,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.323294973949207</v>
       </c>
     </row>
     <row r="924">
@@ -11165,7 +11162,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.21081812104483</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="925">
@@ -11176,7 +11173,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.313613807653738</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="926">
@@ -11187,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.425384018188729</v>
+        <v>-0.664145400808785</v>
       </c>
     </row>
     <row r="927">
@@ -11198,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.241318633392833</v>
+        <v>-0.310085823437393</v>
       </c>
     </row>
     <row r="928">
@@ -11209,7 +11206,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.330301101854716</v>
+        <v>-0.146860896198067</v>
       </c>
     </row>
     <row r="929">
@@ -11220,7 +11217,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.267620830752491</v>
+        <v>-0.207185352605428</v>
       </c>
     </row>
     <row r="930">
@@ -11242,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.14795918367347</v>
+        <v>-11.8500341265458</v>
       </c>
     </row>
     <row r="932">
@@ -11253,7 +11250,7 @@
         <v>16</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.243435813175667</v>
+        <v>-0.165779730908303</v>
       </c>
     </row>
     <row r="933">
@@ -11264,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.295359003450692</v>
+        <v>-0.269880324913887</v>
       </c>
     </row>
     <row r="934">
@@ -11275,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.584751374233067</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="935">
@@ -11286,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.262327814011868</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="936">
@@ -11297,7 +11294,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-2.80864489944084</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="937">
@@ -11319,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.147641854859058</v>
+        <v>-0.844232391348875</v>
       </c>
     </row>
     <row r="939">
@@ -11330,7 +11327,7 @@
         <v>16</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.147959183673469</v>
+        <v>-4.38779458165445</v>
       </c>
     </row>
     <row r="940">
@@ -11341,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.342054929172864</v>
+        <v>-0.235350886671405</v>
       </c>
     </row>
     <row r="941">
@@ -11352,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>0.0706131279835159</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="942">
@@ -11363,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.514020920353356</v>
+        <v>-0.282335879143052</v>
       </c>
     </row>
     <row r="943">
@@ -11374,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.35835000952571</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="944">
@@ -11385,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.60044018640129</v>
       </c>
     </row>
     <row r="945">
@@ -11396,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>0.0165603944285472</v>
+        <v>0.021489028742515</v>
       </c>
     </row>
     <row r="946">
@@ -11407,7 +11404,7 @@
         <v>16</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.274097326304628</v>
+        <v>-0.260363407389479</v>
       </c>
     </row>
     <row r="947">
@@ -11418,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.158152462491961</v>
+        <v>-0.0239749906649187</v>
       </c>
     </row>
     <row r="948">
@@ -11429,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.64463716822395</v>
+        <v>-0.990148193546688</v>
       </c>
     </row>
     <row r="949">
@@ -11440,7 +11437,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>0.239153200806621</v>
+        <v>0.0220426613318896</v>
       </c>
     </row>
     <row r="950">
@@ -11462,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>0.223556668420001</v>
+        <v>0.0822979910328921</v>
       </c>
     </row>
     <row r="952">
@@ -11473,7 +11470,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.506415440123443</v>
+        <v>-4.42255519644416</v>
       </c>
     </row>
     <row r="953">
@@ -11484,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.768118130611713</v>
+        <v>-0.503214313928399</v>
       </c>
     </row>
     <row r="954">
@@ -11506,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-3.0689709264195</v>
+        <v>-0.207743092458745</v>
       </c>
     </row>
     <row r="956">
@@ -11517,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.218444373051465</v>
+        <v>-0.248770092609069</v>
       </c>
     </row>
     <row r="957">
@@ -11539,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>0.290560457346461</v>
+        <v>-1.47559774243086</v>
       </c>
     </row>
     <row r="959">
@@ -11583,7 +11580,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.351505132388684</v>
+        <v>-0.225376378429011</v>
       </c>
     </row>
     <row r="963">
@@ -11594,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.182011283139984</v>
+        <v>-0.209469403988813</v>
       </c>
     </row>
     <row r="964">
@@ -11605,7 +11602,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.158848901165877</v>
       </c>
     </row>
     <row r="965">
@@ -11616,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.355711334778551</v>
+        <v>-0.131488864792548</v>
       </c>
     </row>
     <row r="966">
@@ -11627,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.545541523462731</v>
+        <v>-0.787596235528759</v>
       </c>
     </row>
     <row r="967">
@@ -11638,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.703573306531267</v>
+        <v>-1.05981777862936</v>
       </c>
     </row>
     <row r="968">
@@ -11660,7 +11657,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.203581894560895</v>
+        <v>-0.184229546565472</v>
       </c>
     </row>
     <row r="970">
@@ -11671,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.186577987504283</v>
+        <v>-0.168509192710424</v>
       </c>
     </row>
     <row r="971">
@@ -11682,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-1.03262290983179</v>
+        <v>-0.371002353908943</v>
       </c>
     </row>
     <row r="972">
@@ -11704,7 +11701,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.416516746175574</v>
+        <v>-0.497426439570208</v>
       </c>
     </row>
     <row r="974">
@@ -11715,7 +11712,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-1.83652549863146</v>
+        <v>-0.518078574559795</v>
       </c>
     </row>
     <row r="975">
@@ -11748,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.153694310748969</v>
+        <v>-2.06533947147693</v>
       </c>
     </row>
     <row r="978">
@@ -11759,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>0.421236945817438</v>
+        <v>-0.164401680957767</v>
       </c>
     </row>
     <row r="979">
@@ -11770,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-4.28843894227467</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="980">
@@ -11781,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.340274423779069</v>
+        <v>-0.345165848470793</v>
       </c>
     </row>
     <row r="981">
@@ -11792,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.133654059214319</v>
+        <v>-0.301881350193253</v>
       </c>
     </row>
     <row r="982">
@@ -11803,7 +11800,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.659742971597562</v>
+        <v>-1.19553298175412</v>
       </c>
     </row>
     <row r="983">
@@ -11814,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.191080093945077</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="984">
@@ -11825,7 +11822,7 @@
         <v>16</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.496513202053204</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="985">
@@ -11836,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.183307856667302</v>
+        <v>-0.365368910112325</v>
       </c>
     </row>
     <row r="986">
@@ -11847,7 +11844,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-2.27041500105696</v>
+        <v>-0.367869303882426</v>
       </c>
     </row>
     <row r="987">
@@ -11858,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.403577773377029</v>
+        <v>-0.87870863612249</v>
       </c>
     </row>
     <row r="988">
@@ -11869,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.301362340972518</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="989">
@@ -11880,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.435201213625865</v>
+        <v>-0.679166882045203</v>
       </c>
     </row>
     <row r="990">
@@ -11891,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.169874196730148</v>
+        <v>-0.222540689938411</v>
       </c>
     </row>
     <row r="991">
@@ -11902,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.363306014419179</v>
+        <v>-0.658949089509097</v>
       </c>
     </row>
     <row r="992">
@@ -11913,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.285654381033948</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="993">
@@ -11924,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.199798122786502</v>
+        <v>-1.70510095043585</v>
       </c>
     </row>
     <row r="994">
@@ -11946,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.452338833138893</v>
+        <v>-1.40886928977397</v>
       </c>
     </row>
     <row r="996">
@@ -11979,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.174770848015908</v>
+        <v>-0.0830376734124534</v>
       </c>
     </row>
     <row r="999">
@@ -11990,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.15249158245173</v>
+        <v>-1.01088093279071</v>
       </c>
     </row>
     <row r="1000">
@@ -12001,7 +11998,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-1.12110356603962</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="1001">
@@ -12012,7 +12009,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.25614416937687</v>
       </c>
     </row>
     <row r="1002">
@@ -12023,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.387642180461364</v>
+        <v>-0.236490078394395</v>
       </c>
     </row>
     <row r="1003">
@@ -12045,7 +12042,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.818719273505643</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1005">
@@ -12067,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>0.0300487243417017</v>
+        <v>-0.28906914164544</v>
       </c>
     </row>
     <row r="1007">
@@ -12078,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.2439660004696</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1008">
@@ -12111,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.656019891697799</v>
+        <v>-1.05293868879102</v>
       </c>
     </row>
     <row r="1011">
@@ -12133,7 +12130,7 @@
         <v>16</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.275840866791027</v>
+        <v>-0.235855554585955</v>
       </c>
     </row>
     <row r="1013">
@@ -12144,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.951071939304615</v>
       </c>
     </row>
     <row r="1014">
@@ -12155,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.982468272129674</v>
       </c>
     </row>
     <row r="1015">
@@ -12166,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.339410184591802</v>
+        <v>-0.209701434255945</v>
       </c>
     </row>
     <row r="1016">
@@ -12177,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.297527470714989</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1017">
@@ -12188,7 +12185,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.238302638117926</v>
       </c>
     </row>
     <row r="1018">
@@ -12210,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.305941864139744</v>
+        <v>-0.372624502592173</v>
       </c>
     </row>
     <row r="1020">
@@ -12221,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.10492067494028</v>
       </c>
     </row>
     <row r="1021">
@@ -12243,7 +12240,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.356370389964136</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1023">
@@ -12254,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.196757903364374</v>
+        <v>-0.113220763604875</v>
       </c>
     </row>
     <row r="1024">
@@ -12265,7 +12262,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.16474888203152</v>
+        <v>-0.169949025523249</v>
       </c>
     </row>
     <row r="1025">
@@ -12276,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.190507921842779</v>
       </c>
     </row>
     <row r="1026">
@@ -12298,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-1.00354978632568</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1028">
@@ -12309,7 +12306,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.495457580499806</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1029">
@@ -12331,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.431044573174775</v>
+        <v>-0.325307214073319</v>
       </c>
     </row>
     <row r="1031">
@@ -12353,7 +12350,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-1.26105324374161</v>
+        <v>-0.442237932314106</v>
       </c>
     </row>
     <row r="1033">
@@ -12375,7 +12372,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.403376968775132</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1035">
@@ -12397,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.274237497973323</v>
       </c>
     </row>
     <row r="1037">
@@ -12408,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.0855773744048531</v>
+        <v>0.278783428979214</v>
       </c>
     </row>
     <row r="1038">
@@ -12419,7 +12416,7 @@
         <v>16</v>
       </c>
       <c r="C1038" t="n">
-        <v>-0.185627562306493</v>
+        <v>-0.195535234043989</v>
       </c>
     </row>
     <row r="1039">
@@ -12430,7 +12427,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.645045195456167</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1040">
@@ -12441,7 +12438,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.218334775952736</v>
+        <v>-0.200186324366147</v>
       </c>
     </row>
     <row r="1041">
@@ -12452,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.297737454128919</v>
+        <v>-0.237957385078801</v>
       </c>
     </row>
     <row r="1042">
@@ -12463,7 +12460,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.61811091597556</v>
       </c>
     </row>
     <row r="1043">
@@ -12474,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.469347641142394</v>
+        <v>-0.657993351907613</v>
       </c>
     </row>
     <row r="1044">
@@ -12485,7 +12482,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.248931503923913</v>
+        <v>-0.287760919228699</v>
       </c>
     </row>
     <row r="1045">
@@ -12507,7 +12504,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.0150608000481183</v>
+        <v>-0.166557882325274</v>
       </c>
     </row>
     <row r="1047">
@@ -12518,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.33736685804457</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1048">
@@ -12529,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.616464028140915</v>
+        <v>-0.369037234034514</v>
       </c>
     </row>
     <row r="1049">
@@ -12551,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.386543151566505</v>
+        <v>-0.307698870740364</v>
       </c>
     </row>
     <row r="1051">
@@ -12562,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.396079899706969</v>
       </c>
     </row>
     <row r="1052">
@@ -12584,7 +12581,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.804141106596812</v>
       </c>
     </row>
     <row r="1054">
@@ -12606,7 +12603,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.661470346676438</v>
+        <v>-0.386814499838313</v>
       </c>
     </row>
     <row r="1056">
@@ -12650,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-1.37186976206708</v>
+        <v>-0.183364896475659</v>
       </c>
     </row>
     <row r="1060">
@@ -12661,7 +12658,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.337949329966364</v>
+        <v>-0.219545436979548</v>
       </c>
     </row>
     <row r="1061">
@@ -12672,7 +12669,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.187968418174328</v>
+        <v>-0.243033894219825</v>
       </c>
     </row>
     <row r="1062">
@@ -12683,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.238614235233833</v>
       </c>
     </row>
     <row r="1063">
@@ -12694,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>0.392724857545766</v>
+        <v>-0.143457787969896</v>
       </c>
     </row>
     <row r="1064">
@@ -12705,7 +12702,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.163017632711588</v>
+        <v>-0.647947419419243</v>
       </c>
     </row>
     <row r="1065">
@@ -12727,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.110773687821129</v>
+        <v>-0.0930941219179473</v>
       </c>
     </row>
     <row r="1067">
@@ -12760,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.159763313609468</v>
+        <v>-3.35188475928063</v>
       </c>
     </row>
     <row r="1070">
@@ -12782,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.234374252601774</v>
+        <v>-0.0205227351913675</v>
       </c>
     </row>
     <row r="1072">
@@ -12793,7 +12790,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.232806173519368</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1073">
@@ -12804,7 +12801,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.935181755127603</v>
       </c>
     </row>
     <row r="1074">
@@ -12815,7 +12812,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.214619138581205</v>
+        <v>-0.217831425124652</v>
       </c>
     </row>
     <row r="1075">
@@ -12848,7 +12845,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-2.0565442631894</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1078">
@@ -12903,7 +12900,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.213373723288803</v>
+        <v>-0.224676636809708</v>
       </c>
     </row>
     <row r="1083">
@@ -12914,7 +12911,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.688101679157945</v>
+        <v>-0.181876029855614</v>
       </c>
     </row>
     <row r="1084">
@@ -12925,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.974922309362581</v>
       </c>
     </row>
     <row r="1085">
@@ -12936,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.454098035230862</v>
+        <v>-0.487883746002409</v>
       </c>
     </row>
     <row r="1086">
@@ -12947,7 +12944,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.348542061303438</v>
+        <v>-0.281152208796061</v>
       </c>
     </row>
     <row r="1087">
@@ -12958,7 +12955,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.549545437947511</v>
+        <v>-1.51083104157757</v>
       </c>
     </row>
     <row r="1088">
@@ -12969,7 +12966,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>0.0767949632168685</v>
+        <v>0.0791586618383702</v>
       </c>
     </row>
     <row r="1089">
@@ -12980,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.200317702972926</v>
+        <v>-0.215794897073314</v>
       </c>
     </row>
     <row r="1090">
@@ -12991,7 +12988,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.996042821656557</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1091">
@@ -13013,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.24704227900072</v>
+        <v>-2.23102692035595</v>
       </c>
     </row>
     <row r="1093">
@@ -13024,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.231998565021327</v>
+        <v>-1.24251189666208</v>
       </c>
     </row>
     <row r="1094">
@@ -13046,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.688389612156384</v>
+        <v>-0.490667883918136</v>
       </c>
     </row>
     <row r="1096">
@@ -13068,7 +13065,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.276057048664036</v>
+        <v>-3.56233256604313</v>
       </c>
     </row>
     <row r="1098">
@@ -13079,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.0180133357348526</v>
+        <v>-0.208139712555948</v>
       </c>
     </row>
     <row r="1099">
@@ -13090,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.17885902512142</v>
+        <v>-0.199724397950711</v>
       </c>
     </row>
     <row r="1100">
@@ -13101,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.179913407683662</v>
+        <v>-1.47589006137839</v>
       </c>
     </row>
     <row r="1101">
@@ -13134,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.0951897400542112</v>
+        <v>0.0437527833660897</v>
       </c>
     </row>
     <row r="1104">
@@ -13145,7 +13142,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.159763313609467</v>
+        <v>-6.77206274746552</v>
       </c>
     </row>
     <row r="1105">
@@ -13156,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.40337374744209</v>
       </c>
     </row>
     <row r="1106">
@@ -13167,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.222573180630148</v>
+        <v>-0.409671577139248</v>
       </c>
     </row>
     <row r="1107">
@@ -13178,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.578585638721952</v>
+        <v>-0.347080912491791</v>
       </c>
     </row>
     <row r="1108">
@@ -13189,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.280826901887517</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1109">
@@ -13200,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-1.46125260040238</v>
+        <v>-0.265777679404587</v>
       </c>
     </row>
     <row r="1110">
@@ -13233,7 +13230,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.35465380909628</v>
       </c>
     </row>
     <row r="1113">
@@ -13244,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.289172696882964</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1114">
@@ -13255,7 +13252,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.50807545585652</v>
       </c>
     </row>
     <row r="1115">
@@ -13266,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.0293980556438667</v>
+        <v>0.47211407345276</v>
       </c>
     </row>
     <row r="1116">
@@ -13288,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.351827937254831</v>
+        <v>-0.294059188993151</v>
       </c>
     </row>
     <row r="1118">
@@ -13310,7 +13307,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.438899002028048</v>
       </c>
     </row>
     <row r="1120">
@@ -13321,7 +13318,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.495538920240112</v>
+        <v>-0.453748106463604</v>
       </c>
     </row>
     <row r="1121">
@@ -13332,7 +13329,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.196262510061451</v>
       </c>
     </row>
     <row r="1122">
@@ -13365,7 +13362,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.297750346661261</v>
       </c>
     </row>
     <row r="1125">
@@ -13376,7 +13373,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.625677477938313</v>
+        <v>0.12059747962206</v>
       </c>
     </row>
     <row r="1126">
@@ -13398,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.432176191948323</v>
+        <v>-0.572226109839259</v>
       </c>
     </row>
     <row r="1128">
@@ -13409,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.154727335925849</v>
+        <v>-0.803666059291253</v>
       </c>
     </row>
     <row r="1129">
@@ -13431,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.349097539213127</v>
+        <v>-0.657684765105176</v>
       </c>
     </row>
     <row r="1131">
@@ -13442,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.301971758871798</v>
+        <v>-0.229579451541567</v>
       </c>
     </row>
     <row r="1132">
@@ -13453,7 +13450,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.0639075956125925</v>
+        <v>-0.232392231612541</v>
       </c>
     </row>
     <row r="1133">
@@ -13464,7 +13461,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.389760841647339</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1134">
@@ -13475,7 +13472,7 @@
         <v>16</v>
       </c>
       <c r="C1134" t="n">
-        <v>-3.98159983213236</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1135">
@@ -13497,7 +13494,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.157854912297135</v>
+        <v>-0.15810762104434</v>
       </c>
     </row>
     <row r="1137">
@@ -13508,7 +13505,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.0391203591885816</v>
+        <v>-0.237730006049636</v>
       </c>
     </row>
     <row r="1138">
@@ -13530,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.404196633978972</v>
+        <v>-0.205745360927653</v>
       </c>
     </row>
     <row r="1140">
@@ -13541,7 +13538,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.457366610407109</v>
       </c>
     </row>
     <row r="1141">
@@ -13552,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-1.04998091019366</v>
+        <v>-0.793323013991378</v>
       </c>
     </row>
     <row r="1142">
@@ -13563,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.171571777460506</v>
+        <v>-0.160566641853082</v>
       </c>
     </row>
     <row r="1143">
@@ -13574,7 +13571,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.242128658446794</v>
+        <v>-0.205541956832285</v>
       </c>
     </row>
     <row r="1144">
@@ -13596,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.464082806433374</v>
       </c>
     </row>
     <row r="1146">
@@ -13607,7 +13604,7 @@
         <v>16</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.380261307185617</v>
+        <v>-0.330767411832066</v>
       </c>
     </row>
     <row r="1147">
@@ -13618,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.500506304177738</v>
+        <v>-0.636786654433715</v>
       </c>
     </row>
     <row r="1148">
@@ -13640,7 +13637,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.433817300946475</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1150">
@@ -13673,7 +13670,7 @@
         <v>16</v>
       </c>
       <c r="C1152" t="n">
-        <v>-0.455285575682051</v>
+        <v>-0.244159170790103</v>
       </c>
     </row>
     <row r="1153">
@@ -13706,7 +13703,7 @@
         <v>16</v>
       </c>
       <c r="C1155" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.343664203633631</v>
       </c>
     </row>
     <row r="1156">
@@ -13717,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.228638468656257</v>
+        <v>-0.720387932238933</v>
       </c>
     </row>
     <row r="1157">
@@ -13739,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.184104631396879</v>
+        <v>-0.12220867411408</v>
       </c>
     </row>
     <row r="1159">
@@ -13761,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.41088354163801</v>
+        <v>-0.604156869526918</v>
       </c>
     </row>
     <row r="1161">
@@ -13772,7 +13769,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.0762276309708946</v>
+        <v>-0.526835235273045</v>
       </c>
     </row>
     <row r="1162">
@@ -13794,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.309629242127363</v>
+        <v>-0.908220208593125</v>
       </c>
     </row>
     <row r="1164">
@@ -13827,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.798186508794993</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1167">
@@ -13838,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.436844727072904</v>
+        <v>-0.322542027551126</v>
       </c>
     </row>
     <row r="1168">
@@ -13849,7 +13846,7 @@
         <v>16</v>
       </c>
       <c r="C1168" t="n">
-        <v>-0.19159282103857</v>
+        <v>-0.211579385518562</v>
       </c>
     </row>
     <row r="1169">
@@ -13871,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.300727805409335</v>
+        <v>0.396388397070529</v>
       </c>
     </row>
     <row r="1171">
@@ -13904,7 +13901,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.398980819560274</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1174">
@@ -13926,7 +13923,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.226229564493493</v>
+        <v>-0.385732191782472</v>
       </c>
     </row>
     <row r="1176">
@@ -13937,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.62196771742632</v>
       </c>
     </row>
     <row r="1177">
@@ -13959,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.234839393931191</v>
+        <v>-0.233548898231149</v>
       </c>
     </row>
     <row r="1179">
@@ -13970,7 +13967,7 @@
         <v>16</v>
       </c>
       <c r="C1179" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.27938440519781</v>
       </c>
     </row>
     <row r="1180">
@@ -13981,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.440841802006281</v>
+        <v>-0.423365063101233</v>
       </c>
     </row>
     <row r="1181">
@@ -14014,7 +14011,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.492775355017102</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1184">
@@ -14025,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.103413512766392</v>
+        <v>-0.0282236198275232</v>
       </c>
     </row>
     <row r="1185">
@@ -14036,7 +14033,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.461488404054955</v>
+        <v>-0.0972741877487853</v>
       </c>
     </row>
     <row r="1186">
@@ -14047,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.369492420224861</v>
+        <v>0.522790210753669</v>
       </c>
     </row>
     <row r="1187">
@@ -14058,7 +14055,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.344994284566369</v>
+        <v>-0.26274800327394</v>
       </c>
     </row>
     <row r="1188">
@@ -14080,7 +14077,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.210292206645973</v>
+        <v>-1.79443584889682</v>
       </c>
     </row>
     <row r="1190">
@@ -14091,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.387856932523354</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1191">
@@ -14102,7 +14099,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.322075135882361</v>
       </c>
     </row>
     <row r="1192">
@@ -14124,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-3.64446121181302</v>
+        <v>-0.85183137899553</v>
       </c>
     </row>
     <row r="1194">
@@ -14135,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.728721592892074</v>
+        <v>-0.72051468288973</v>
       </c>
     </row>
     <row r="1195">
@@ -14157,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.144574283307136</v>
+        <v>0.0509676823987846</v>
       </c>
     </row>
     <row r="1197">
@@ -14168,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.328214067514704</v>
+        <v>0.00652273542340687</v>
       </c>
     </row>
     <row r="1198">
@@ -14179,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.146265803200973</v>
+        <v>-0.129135464932614</v>
       </c>
     </row>
     <row r="1199">
@@ -14190,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.227009191399247</v>
+        <v>-0.99190867793476</v>
       </c>
     </row>
     <row r="1200">
@@ -14201,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.298883968935924</v>
+        <v>-0.175921496805931</v>
       </c>
     </row>
     <row r="1201">
@@ -14212,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.373237903160279</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
   </sheetData>
@@ -14274,7 +14271,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>3.29808842378047</v>
+        <v>3.73071428571428</v>
       </c>
     </row>
     <row r="4">
@@ -14291,7 +14288,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>4.23357142857143</v>
+        <v>2.4954546786833</v>
       </c>
     </row>
     <row r="5">
@@ -14410,7 +14407,7 @@
         <v>-4.09</v>
       </c>
       <c r="E11" t="n">
-        <v>5.50357142857143</v>
+        <v>5.01135219294017</v>
       </c>
     </row>
     <row r="12">
@@ -14444,7 +14441,7 @@
         <v>-1.86</v>
       </c>
       <c r="E13" t="n">
-        <v>8.99614707249766</v>
+        <v>5.34428571428571</v>
       </c>
     </row>
     <row r="14">
@@ -14495,7 +14492,7 @@
         <v>-0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>5.24571428571428</v>
+        <v>5.68316349134932</v>
       </c>
     </row>
     <row r="17">
@@ -15022,7 +15019,7 @@
         <v>1.706</v>
       </c>
       <c r="E47" t="n">
-        <v>1.47500490768417</v>
+        <v>1.99364285714286</v>
       </c>
     </row>
     <row r="48">
@@ -15039,7 +15036,7 @@
         <v>4.218</v>
       </c>
       <c r="E48" t="n">
-        <v>2.24241134399582</v>
+        <v>1.81421428571429</v>
       </c>
     </row>
     <row r="49">
@@ -15056,7 +15053,7 @@
         <v>1.578</v>
       </c>
       <c r="E49" t="n">
-        <v>1.25341081855677</v>
+        <v>2.00278571428571</v>
       </c>
     </row>
     <row r="50">
@@ -15073,7 +15070,7 @@
         <v>3.683</v>
       </c>
       <c r="E50" t="n">
-        <v>4.86665192143637</v>
+        <v>1.85242857142857</v>
       </c>
     </row>
     <row r="51">
@@ -15090,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>4.96802863705156</v>
+        <v>1.90242857142857</v>
       </c>
     </row>
     <row r="52">
@@ -15107,7 +15104,7 @@
         <v>2.44</v>
       </c>
       <c r="E52" t="n">
-        <v>2.82186657426693</v>
+        <v>1.94121428571429</v>
       </c>
     </row>
     <row r="53">
@@ -15124,7 +15121,7 @@
         <v>3.879</v>
       </c>
       <c r="E53" t="n">
-        <v>5.94613871843194</v>
+        <v>1.83842857142857</v>
       </c>
     </row>
     <row r="54">
@@ -15141,7 +15138,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E54" t="n">
-        <v>1.63542349147712</v>
+        <v>2.07407142857143</v>
       </c>
     </row>
     <row r="55">
@@ -15158,7 +15155,7 @@
         <v>-1.918</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.76309695230822</v>
+        <v>2.2525</v>
       </c>
     </row>
     <row r="56">
@@ -15175,7 +15172,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>1.24073761223053</v>
+        <v>2.0675</v>
       </c>
     </row>
     <row r="57">
@@ -15192,7 +15189,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E57" t="n">
-        <v>0.11744764656904</v>
+        <v>-0.768366787281454</v>
       </c>
     </row>
     <row r="58">
@@ -15209,7 +15206,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>4.20301836896375</v>
+        <v>1.752</v>
       </c>
     </row>
     <row r="59">
@@ -15226,7 +15223,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>1.65684787992998</v>
+        <v>5.39728423570562</v>
       </c>
     </row>
     <row r="60">
@@ -15243,7 +15240,7 @@
         <v>1.311</v>
       </c>
       <c r="E60" t="n">
-        <v>1.78880836706362</v>
+        <v>2.02185714285714</v>
       </c>
     </row>
     <row r="61">
@@ -15260,7 +15257,7 @@
         <v>2.862</v>
       </c>
       <c r="E61" t="n">
-        <v>1.40570679266462</v>
+        <v>1.91107142857143</v>
       </c>
     </row>
     <row r="62">
@@ -15311,7 +15308,7 @@
         <v>90</v>
       </c>
       <c r="E64" t="n">
-        <v>8.51319227932427</v>
+        <v>37.8571428571429</v>
       </c>
     </row>
     <row r="65">
@@ -15795,10 +15792,10 @@
         <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -15812,10 +15809,10 @@
         <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -15843,13 +15840,13 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -15860,13 +15857,13 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -15877,13 +15874,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.866666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -15894,13 +15891,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.866666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -15911,13 +15908,13 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.266666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -15928,13 +15925,13 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.266666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -15945,13 +15942,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.266666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -15962,13 +15959,13 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.266666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -15979,13 +15976,13 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0.266666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -15996,13 +15993,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.266666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -16016,196 +16013,9 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>
